--- a/results/Int Task Remove ACC -0.1/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.002516778523489882 +/- 0.0014875275341813203</t>
+          <t>0.003590604026845656 +/- 0.0007948133746528064</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.028154362416107314 +/- 0.0015189893017122501</t>
+          <t>-0.020906040268456348 +/- 0.0011434043649262223</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0017785234899329373 +/- 0.0012470405487289941</t>
+          <t>0.004630872483221515 +/- 0.0015289645301872004</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.001510067114094027 +/- 0.0014799380584698044</t>
+          <t>0.0021476510067114153 +/- 0.001239341296148946</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.001778523489932926 +/- 0.0017114093959731454</t>
+          <t>-0.00318791946308723 +/- 0.0016319216665486845</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.005805369127516735 +/- 0.0010072705382418712</t>
+          <t>0.009496644295302037 +/- 0.0018746949964380576</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.00030014335268454254</t>
+          <t>0.0003691275167785224 +/- 0.0003165765480555844</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0030872483221475954 +/- 0.00137379124097037</t>
+          <t>-0.0006375838926174438 +/- 0.0012140974842366273</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.03802013422818797 +/- 0.0024843549018630294</t>
+          <t>0.0439597315436242 +/- 0.003176418675489738</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.05842281879194635 +/- 0.004160126542964187</t>
+          <t>0.06238255033557048 +/- 0.0030031213586349578</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.007348993288590655 +/- 0.0007570814880992188</t>
+          <t>0.0034899328859060775 +/- 0.001084261370564</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0012080536912752239 +/- 0.0017769399053521812</t>
+          <t>0.0022483221476510273 +/- 0.0014476278261827576</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-3.355704697981521e-05 +/- 0.0008935252990398811</t>
+          <t>0.0020469798657718474 +/- 0.002177074038028003</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.04805369127516783 +/- 0.0021891954940000216</t>
+          <t>0.0409060402684564 +/- 0.0026864506791443457</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0008389261744965904 +/- 0.0027064959800576177</t>
+          <t>0.006241610738255077 +/- 0.0022269342312801364</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0012416107382550723 +/- 0.0009257123640358284</t>
+          <t>0.0018456375838926565 +/- 0.0010095039568114976</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0034228187919463694 +/- 0.0009817945529079024</t>
+          <t>-0.001208053691275146 +/- 0.0011546745324889384</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0009395973154362914 +/- 0.0011797581094796592</t>
+          <t>0.001577181208053713 +/- 0.0012560380719606027</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-0.0035234899328858704 +/- 0.0011453723601259065</t>
+          <t>-0.0003691275167785002 +/- 0.0015263846195361017</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.00023489932885902842 +/- 0.00021486994085343443</t>
+          <t>-0.0005033557046979608 +/- 0.0003093806864863299</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.005604026845637633 +/- 0.0015599515837811339</t>
+          <t>0.018187919463087288 +/- 0.0018428899621135664</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.008892617449664386 +/- 0.001554165929786497</t>
+          <t>-0.005838926174496617 +/- 0.0015392409317019989</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0022818791946309313 +/- 0.0009103798635067343</t>
+          <t>-0.002550335570469753 +/- 0.0019053784653125423</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0013422818791945846 +/- 0.0009128503697137962</t>
+          <t>-0.0004697986577180902 +/- 0.00131858273183815</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.00010067114093956775 +/- 0.000765953839631769</t>
+          <t>-0.00013422818791943846 +/- 0.0016925530487138934</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.00010067114093955664 +/- 0.0003691275167785325</t>
+          <t>-0.0005369127516778205 +/- 0.0006040268456375927</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.0010067114093959106 +/- 0.004167023241953124</t>
+          <t>-0.0033557046979865502 +/- 0.002684563758389255</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.016174496644295256 +/- 0.0018911413159201868</t>
+          <t>-0.014597315436241588 +/- 0.0016862207417988127</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.00647651006711405 +/- 0.0019454406765954133</t>
+          <t>-0.007852348993288539 +/- 0.001441000708294215</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.002919463087248253 +/- 0.0014860127399654018</t>
+          <t>-0.010100671140939576 +/- 0.0016194534915454485</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0006711409395973699 +/- 0.0007351980637653255</t>
+          <t>0.0002013422818792243 +/- 0.0006223905030534109</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0006711409395973811 +/- 0.00045021502902680343</t>
+          <t>-0.0002013422818791577 +/- 0.0004026845637583617</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.006174496644295246 +/- 0.0015319076792635281</t>
+          <t>-0.007651006711409359 +/- 0.0008594797634138322</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.010302013422818734 +/- 0.0012649715989913434</t>
+          <t>-0.00912751677852346 +/- 0.001729409225063797</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0005704697986576801 +/- 0.0004257911926325069</t>
+          <t>-0.00026845637583888804 +/- 0.0005155131374408253</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.00046979865771810123 +/- 0.0006223905030534</t>
+          <t>-0.0023154362416107134 +/- 0.0007110610771952132</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0017449664429530555 +/- 0.0013489765934390483</t>
+          <t>-0.002785234899328837 +/- 0.0015527161478200322</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.0009060402684563429 +/- 0.0010616974509769454</t>
+          <t>-0.007013422818791903 +/- 0.0012773735778975818</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0008724832214765832 +/- 0.0005022358908421471</t>
+          <t>-0.0005033557046979498 +/- 0.0006753225435401997</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0005033557046979387 +/- 0.0009281420594590299</t>
+          <t>0.0004362416107382749 +/- 0.0011821419432086156</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0006040268456375508 +/- 0.0008724832214765141</t>
+          <t>-0.009060402684563717 +/- 0.0010925382950402326</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.0030872483221476175 +/- 0.0020067001862719446</t>
+          <t>-0.00614093959731542 +/- 0.0017823183523341627</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0011409395973154823 +/- 0.0010842613705640042</t>
+          <t>-0.005805369127516747 +/- 0.001637432603859846</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.00785234899328865 +/- 0.0008247117937882198</t>
+          <t>0.007818791946308756 +/- 0.0017504431349993396</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0005369127516778094 +/- 0.0009153142078514028</t>
+          <t>0.0001677852348993536 +/- 0.001074349704267245</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0007382550335569782 +/- 0.0012627441424313283</t>
+          <t>-0.004932885906040252 +/- 0.0017048168853530964</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.00046979865771807906 +/- 0.00026845637583892414</t>
+          <t>0.00030201342281881426 +/- 0.0006786492757099506</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.0013422818791946622 +/- 0.0011624502064220637</t>
+          <t>0.0005033557046980053 +/- 0.001409795405208065</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.007785234899328896 +/- 0.0014221221543903983</t>
+          <t>0.004899328859060437 +/- 0.0011643860116038536</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.00248322147651 +/- 0.0017705914037950306</t>
+          <t>-0.00030201342281875875 +/- 0.0011275367527792868</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.0017785234899328373 +/- 0.0017696371642194919</t>
+          <t>-0.0010402684563758035 +/- 0.00154835865705493</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.00023489932885902842 +/- 0.0005821930058019326</t>
+          <t>0.0003355704697986961 +/- 0.0007038985558188969</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.001208053691275124 +/- 0.0005022358908421322</t>
+          <t>-0.0012416107382550168 +/- 0.0004988613673596922</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.0010738255033557742 +/- 0.0002511179454210713</t>
+          <t>-0.0006711409395972811 +/- 0.0004745683095211643</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-0.011610738255033504 +/- 0.001352311522121457</t>
+          <t>-0.0004026845637583487 +/- 0.0013572985514199248</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.001174496644295242 +/- 0.001248845239324051</t>
+          <t>0.0021140939597315777 +/- 0.0008757039161543543</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.0008389261744966125 +/- 0.0007236194178808083</t>
+          <t>-0.0006375838926174215 +/- 0.0010228020573240394</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.004060402684563802 +/- 0.001489040787404929</t>
+          <t>0.0034899328859060775 +/- 0.0009275352322875818</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.002684563758389313 +/- 0.0018982732380846904</t>
+          <t>-0.004228187919463067 +/- 0.0010200459163470206</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.0009060402684563318 +/- 0.00047575325096501324</t>
+          <t>-3.355704697983741e-05 +/- 0.0006446098225603292</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.0007382550335571003 +/- 0.0007769018055563952</t>
+          <t>-0.002550335570469775 +/- 0.0006575811390022052</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.0033892617449663765 +/- 0.0013207160170573388</t>
+          <t>-0.0011744966442952753 +/- 0.001783581512203794</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.011140939597315469 +/- 0.0015509020145357464</t>
+          <t>0.005335570469798689 +/- 0.0015263846195361077</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.0011409395973154823 +/- 0.001144880678471933</t>
+          <t>0.00023489932885908393 +/- 0.0009731543624160927</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.00046979865771817897 +/- 0.0004551899317533868</t>
+          <t>0.00020134228187923542 +/- 0.0003075554157688379</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.005536912751677803 +/- 0.0014017851392084117</t>
+          <t>-0.005838926174496606 +/- 0.0009632684627118936</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.007651006711409347 +/- 0.0012265548243286723</t>
+          <t>0.0010067114093960216 +/- 0.00116245020642207</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0007046979865771297 +/- 0.0007862667458966283</t>
+          <t>-0.0011409395973154158 +/- 0.0006040268456375915</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.011744966442953064 +/- 0.0019681715837067343</t>
+          <t>0.007751677852349037 +/- 0.0018161153191590253</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.0006711409395973699 +/- 0.0015230611701893</t>
+          <t>-0.001006711409395944 +/- 0.0008081607099860687</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.002718120805369073 +/- 0.0009425887184690195</t>
+          <t>0.010302013422818824 +/- 0.0016026783807059906</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-0.0005369127516778094 +/- 0.00030755541576884036</t>
+          <t>0.00046979865771813457 +/- 0.00030755541576884523</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.00020134228187923542 +/- 0.00047929049855994214</t>
+          <t>-0.0011409395973154047 +/- 0.0006575811390022142</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.0001677852348993758 +/- 0.00045642518485690425</t>
+          <t>-0.00016778523489929809 +/- 0.00040408035499302046</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.0006711409395972701 +/- 0.00039705233443622747</t>
+          <t>0.0017785234899328928 +/- 0.0006012239217170852</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.00023489932885910613 +/- 0.0009846577685316312</t>
+          <t>0.005939597315436263 +/- 0.001424100347243164</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-0.00023489932885901733 +/- 0.00015377770788439595</t>
+          <t>-0.0002013422818791688 +/- 0.00022259226780906984</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.000973154362416162 +/- 0.000661848420245524</t>
+          <t>0.003724832214765117 +/- 0.0009777719653914988</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0026845637583892135 +/- 0.0008219764237527477</t>
+          <t>-0.005268456375838904 +/- 0.0013921119807175507</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0013087248322148249 +/- 0.0011859461105417565</t>
+          <t>-0.0005369127516778426 +/- 0.0009748885265996108</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5.551115123125783e-17 +/- 0.0006541472714636999</t>
+          <t>-0.001107382550335534 +/- 0.0009010551397380888</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.006275167785234859 +/- 0.0013000919884436613</t>
+          <t>-0.0013422818791946067 +/- 0.001415773363069055</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.002818791946308785 +/- 0.001986395783483071</t>
+          <t>0.009899328859060419 +/- 0.0012931442193286988</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0005369127516778982 +/- 0.0009977227347193634</t>
+          <t>-0.0012751677852348765 +/- 0.0008724832214765157</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.002185981956974281 +/- 0.0014725256886830484</t>
+          <t>0.0003122831367105783 +/- 0.0009869162146653352</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0013185287994448513 +/- 0.0009021512838306877</t>
+          <t>-0.0010756419153366004 +/- 0.001578288052122713</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0010756419153366004 +/- 0.0017655175896195184</t>
+          <t>0.003018736988202575 +/- 0.0009820244065291558</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.000520471894517649 +/- 0.0018311276616181289</t>
+          <t>0.001145038167938861 +/- 0.0015675721024394759</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.002567661346287242 +/- 0.0012433360768333741</t>
+          <t>0.004337265787647415 +/- 0.0014659701717055953</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.006523247744621763 +/- 0.0017882163395871056</t>
+          <t>0.0120749479528105 +/- 0.0016480696859178163</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.000346981263011803</t>
+          <t>-0.0003816793893130055 +/- 0.00042354460845707144</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.005065926439972201 +/- 0.0018890572642354293</t>
+          <t>0.003018736988202575 +/- 0.001298748596267398</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.03188757807078415 +/- 0.004630477630286532</t>
+          <t>-0.005100624566273471 +/- 0.0046811617566965774</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.013185287994448281 +/- 0.004149292416065731</t>
+          <t>-0.01943095072866069 +/- 0.003153523321999105</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.004614850798056869 +/- 0.0017421776836409988</t>
+          <t>-0.00232477446217908 +/- 0.0010062456627342286</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.002394170714781441 +/- 0.001674521653298244</t>
+          <t>0.00607217210270643 +/- 0.0009721669483776454</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.000104094378903552 +/- 0.0009316947662801842</t>
+          <t>0.0003122831367105672 +/- 0.002072904515092821</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.007217210270645424 +/- 0.003381242946587039</t>
+          <t>0.01936155447605824 +/- 0.002548836595726156</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.013671061762664838 +/- 0.002281649163466153</t>
+          <t>0.008154059680777181 +/- 0.002134710397678278</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.004129077029840433 +/- 0.0014839281596351831</t>
+          <t>0.002081887578070718 +/- 0.0011189809504925095</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0019083969465649164 +/- 0.0008100359146376782</t>
+          <t>0.003365718251214378 +/- 0.0010977995849796413</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.0005551700208188959 +/- 0.0012625541567425546</t>
+          <t>-0.0017696044413602063 +/- 0.0016600796271902375</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.001700208188757857 +/- 0.001928479282663453</t>
+          <t>-0.001006245662734251 +/- 0.0011658776971832927</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.00010409437890354089 +/- 0.00046681554639396</t>
+          <t>-0.0001734906315059237 +/- 0.0004968015636112237</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0007980569049271691 +/- 0.002651854101913303</t>
+          <t>0.004545454545454486 +/- 0.0031129847074749476</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.010235947258847966 +/- 0.0012913111773718735</t>
+          <t>-0.008848022206800898 +/- 0.0022924408964828473</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.00676613462873008 +/- 0.002018763110033145</t>
+          <t>0.0079458709229701 +/- 0.0008974682273682979</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.93962526023606e-05 +/- 0.00043337945859809153</t>
+          <t>0.004649548924358049 +/- 0.0011103400416377696</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0019430950728660968 +/- 0.0007144781499644114</t>
+          <t>-0.00204718945176966 +/- 0.0015782880521227067</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0004510756419153217 +/- 0.0006216680384166634</t>
+          <t>-0.0006592643997224256 +/- 0.00045107564191534385</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.017140874392782824 +/- 0.0021624478072009546</t>
+          <t>0.013705759888965963 +/- 0.0019020777340271512</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.01891047883414293 +/- 0.0011323503728022889</t>
+          <t>-0.010617626648161039 +/- 0.002030359311357078</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.012734212352532937 +/- 0.0015365433605471607</t>
+          <t>-0.005031228313671132 +/- 0.0011741099455717312</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.012179042331714064 +/- 0.0018059699763599327</t>
+          <t>-0.012664816099930653 +/- 0.0015144450272584907</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.00038167938931297216 +/- 0.000629367007190036</t>
+          <t>0.000936849410131757 +/- 0.0005605653858918729</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0014573213046495726 +/- 0.0007570237414736913</t>
+          <t>-0.0015614156835531134 +/- 0.0004968015636112625</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.011485079805690445 +/- 0.0017518258933191353</t>
+          <t>-0.008709229701596155 +/- 0.0012164155546813369</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.019118667591950012 +/- 0.0017518258933191594</t>
+          <t>-0.00634975711311595 +/- 0.001388358710877322</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0007286606523247751 +/- 0.000477020370744867</t>
+          <t>-1.1102230246251566e-17 +/- 0.00015517473820260015</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.002081887578070751 +/- 0.0014051670181343655</t>
+          <t>0.0024982650936848706 +/- 0.0007077056923793016</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0030881332408050355 +/- 0.0010801098137594217</t>
+          <t>-0.001492019430950764 +/- 0.0015207916031097302</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.01061762664816096 +/- 0.0016363395034769822</t>
+          <t>-0.004337265787647537 +/- 0.0011638105365196873</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.0005551700208188848 +/- 0.0006049825043082226</t>
+          <t>-0.0009715475364330484 +/- 0.0003399708178741454</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.005274115197779361 +/- 0.0010151796556785162</t>
+          <t>0.004406662040249787 +/- 0.0012515398193526529</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.011103400416377474 +/- 0.0013167013158230801</t>
+          <t>-0.0017696044413601953 +/- 0.0014260043433750764</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0007286606523247419 +/- 0.001196456603023336</t>
+          <t>0.006696738376127653 +/- 0.0019322214840146769</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.008986814712005497 +/- 0.002072904515092831</t>
+          <t>-0.0019083969465649385 +/- 0.0019887203165728155</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.005794587092296988 +/- 0.0017559446119195055</t>
+          <t>-0.003365718251214489 +/- 0.0014643267068708908</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.0021859819569742924 +/- 0.0015286877704309824</t>
+          <t>0.00017349063150583487 +/- 0.0015223741130104098</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.001561415683553058 +/- 0.0011843197894431342</t>
+          <t>-0.0005551700208189403 +/- 0.0016215574525395957</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0015614156835531134 +/- 0.0007319577761876935</t>
+          <t>0.0017696044413600843 +/- 0.0005250779302714018</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.003053435114503866 +/- 0.0012777205162749666</t>
+          <t>0.001839000693962467 +/- 0.0014887881993702187</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0006592643997223923 +/- 0.0013478781817872867</t>
+          <t>0.008848022206800777 +/- 0.0014073074108725287</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.002775850104094424 +/- 0.001463915552375387</t>
+          <t>-0.0014573213046495948 +/- 0.0016842000138114581</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.006488549618320583 +/- 0.0014643267068708548</t>
+          <t>-0.002775850104094424 +/- 0.001387925052047212</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.001353226925745976 +/- 0.0008130030890950445</t>
+          <t>-0.0011103400416377696 +/- 0.00033997081787414546</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.00010409437890352979 +/- 0.0005816465861984654</t>
+          <t>-0.0009715475364330706 +/- 0.0009665779512271969</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.0021512838306730784 +/- 0.0007409492194331086</t>
+          <t>-0.001526717557251933 +/- 0.0006974237072256108</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.009437890353920864 +/- 0.0018736988202636934</t>
+          <t>0.00031228313671054496 +/- 0.0014090173840559793</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.003573907009021471 +/- 0.001796612556002734</t>
+          <t>-0.0008327550312283605 +/- 0.0016870570133439508</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0004510756419153439 +/- 0.0002710010296983616</t>
+          <t>0.0003122831367105561 +/- 0.0009107845071760065</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.0001734906315059015 +/- 0.0008392357128693978</t>
+          <t>-0.001387925052047223 +/- 0.0012218471104551746</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.009472588480222022 +/- 0.0016425815931359617</t>
+          <t>0.00010409437890348538 +/- 0.0008218403388151673</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.0016655100624565877 +/- 0.0006546829376860615</t>
+          <t>-0.0004857737682165575 +/- 0.0008667589171961466</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.0006245662734212121 +/- 0.0012198747974494525</t>
+          <t>0.0037820957668285526 +/- 0.0018126242729505908</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.000693962526023617 +/- 0.002306838325967324</t>
+          <t>-0.0006939625260236393 +/- 0.001251058735414269</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.007217210270645369 +/- 0.0015733218665863328</t>
+          <t>-0.011346287300485836 +/- 0.001151329633798541</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.0027411519777931436 +/- 0.0008974682273683184</t>
+          <t>-0.004892435808466411 +/- 0.0009496136143930525</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-0.0003816793893129833 +/- 0.0002428868841082621</t>
+          <t>-0.00020818875780708178 +/- 0.0002775850104094424</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.00020818875780705958 +/- 0.0011838113885657107</t>
+          <t>0.004094378903539153 +/- 0.0020632989239859276</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.00048577376821654636 +/- 0.0020004906738930765</t>
+          <t>-0.0034351145038168497 +/- 0.001080109813759447</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.0005898681471200428 +/- 0.0005605653858918412</t>
+          <t>-0.001977793199167277 +/- 0.0007609893198980452</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.00013879250520469898 +/- 0.0013634200350026565</t>
+          <t>0.003851492019430902 +/- 0.0017030383333529807</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.00031228313671064487 +/- 0.0014260043433750472</t>
+          <t>0.001492019430950664 +/- 0.0013796596358133949</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-0.006523247744621774 +/- 0.0013420596534221797</t>
+          <t>-0.002428868841082632 +/- 0.0014221999675169451</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>3.46981263011803e-05 +/- 0.0001040943789035409</t>
+          <t>0.0001734906315058571 +/- 0.00023276210730388785</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.0012838306731436711 +/- 0.0006592643997224257</t>
+          <t>-0.000693962526023617 +/- 0.0005146563835597127</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0002081887578070929 +/- 0.0009715475364330221</t>
+          <t>-0.0006245662734212676 +/- 0.0009540407414897543</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.0002428868841082621 +/- 0.00041201742147946253</t>
+          <t>-0.00041637751561416356 +/- 0.0004603226634775092</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.0015961138098542938 +/- 0.0011318186280569295</t>
+          <t>-0.0024635669673838123 +/- 0.0012649358871310288</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0008327550312283271 +/- 0.000643554371651343</t>
+          <t>0.0014226231783482813 +/- 0.0006843540223218715</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.0018736988202636474 +/- 0.001223816244868025</t>
+          <t>-0.0005551700208189181 +/- 0.0010547317247446455</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0007980569049271136 +/- 0.0016498949934724005</t>
+          <t>0.0016308119361553742 +/- 0.0009445286321177061</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.000727834037592067</t>
+          <t>-0.0001734906315059237 +/- 0.0003879368455065227</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0015614156835530245 +/- 0.0011741099455717132</t>
+          <t>-0.0007286606523248084 +/- 0.0011658776971832882</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-0.0024982650936848814 +/- 0.001138183169108729</t>
+          <t>-0.0014573213046495948 +/- 0.0011898978625594753</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0017349063150589594 +/- 0.001150806658693733</t>
+          <t>0.0032963219986120174 +/- 0.0012144344205413105</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0032974661575841833 +/- 0.0007644122022056732</t>
+          <t>-0.008816383200277644 +/- 0.0014328196765394016</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.0041652204095799835 +/- 0.0017630579797570792</t>
+          <t>-0.01502950364456781 +/- 0.0011621429394504169</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.003054494967025356 +/- 0.0010954344906670822</t>
+          <t>0.0023255813953488636 +/- 0.0016865714145444341</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.0025338424158278137 +/- 0.0016284212573050919</t>
+          <t>0.0027073932662270315 +/- 0.0015966678236723458</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0005900728913571518 +/- 0.0011826952473030451</t>
+          <t>-0.004165220409579962 +/- 0.0016056971199195297</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.000867754251995867 +/- 0.0022400836931985605</t>
+          <t>0.007601527247483553 +/- 0.0014598917629165588</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0004165220409579895 +/- 0.0006170214798552829</t>
+          <t>0.00027768136063865967 +/- 0.00020826102047899478</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.006699062825407842 +/- 0.000982365268870893</t>
+          <t>-0.013293995140576165 +/- 0.0019014711454081827</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.015931968066643543 +/- 0.0024614870741397304</t>
+          <t>0.009649427282193724 +/- 0.002628822801632969</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.026900381811870877 +/- 0.0017783670194306846</t>
+          <t>0.016209649427282223 +/- 0.0036833689346032154</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.007740367927802827 +/- 0.0013536966331135025</t>
+          <t>-0.02138146476917733 +/- 0.0013550309820161799</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0010065949323151747 +/- 0.001984559855456126</t>
+          <t>0.004408191600138889 +/- 0.0024741802689617143</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.010656022214508865 +/- 0.0014893049602863586</t>
+          <t>0.008156889968760895 +/- 0.0014746716963726534</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.04484553974314472 +/- 0.002160969443425653</t>
+          <t>-0.04311003123915304 +/- 0.0033031245410261186</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.006421381464769183 +/- 0.002043188150331321</t>
+          <t>0.004998264491496052 +/- 0.0023294636217372493</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.0005206525511974758 +/- 0.0015149706937032173</t>
+          <t>0.008955223880597041 +/- 0.0013335211879415927</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0014578271433530077 +/- 0.0013953315683611165</t>
+          <t>-0.003019784796945468 +/- 0.0015526740191839701</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.017424505380076373 +/- 0.0015738679692821383</t>
+          <t>-0.018361679972231836 +/- 0.0018396390142311563</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.0015966678236723486 +/- 0.0011532973082843685</t>
+          <t>-0.0007983339118361355 +/- 0.0010533836102390413</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.00027768136063865967 +/- 0.00013884068031932983</t>
+          <t>-0.00013884068031932983 +/- 0.00023024122112844922</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.001735508503991645 +/- 0.002464177625727011</t>
+          <t>-0.009614717112113803 +/- 0.0022443822506528523</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.00777507809788266 +/- 0.0012043978877402056</t>
+          <t>-0.010621312044429 +/- 0.002385677233938164</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0007636237417563363 +/- 0.0010389885142031078</t>
+          <t>0.004790003471017046 +/- 0.00208145287755153</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0006594932315168167 +/- 0.0013029034626256823</t>
+          <t>0.001180145782714359 +/- 0.0013189864630336772</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0010760152724748062 +/- 0.001046498676270804</t>
+          <t>-0.003575147518222821 +/- 0.0017219183276379682</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.00027768136063865967 +/- 0.0005553627212773193</t>
+          <t>0.00065949323151685 +/- 0.0007019697471765864</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.002464422075668182 +/- 0.0018132534379186219</t>
+          <t>0.01617493925720239 +/- 0.002698478545723966</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.011697327316903839 +/- 0.0019077967488595974</t>
+          <t>-0.020444290177021852 +/- 0.0017247147863665112</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.005032974661575829 +/- 0.0012148559527941567</t>
+          <t>-0.014161749392571976 +/- 0.0020405329339394864</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0015272474835126392 +/- 0.001553837506810105</t>
+          <t>-0.01294689343977783 +/- 0.0010418834446236386</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0005900728913571518 +/- 0.0004121604334271988</t>
+          <t>0.0004165220409580228 +/- 0.0007079513382287954</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.00020826102047899475 +/- 0.0005421901892333526</t>
+          <t>-0.0005553627212773193 +/- 0.0005421901892333526</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.0032974661575841833 +/- 0.0006810627167771187</t>
+          <t>-0.01308573412009716 +/- 0.0011517292622726125</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.013918778202013172 +/- 0.0018132534379186422</t>
+          <t>-0.024435959736202672 +/- 0.0021010407428561535</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.0010413051023949738 +/- 0.00031045719923633873</t>
+          <t>0.0010413051023950514 +/- 0.0004908759327917981</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0002776813606386708 +/- 0.0008184537398508549</t>
+          <t>-0.0011801457827143147 +/- 0.0011107254425546617</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0005553627212773416 +/- 0.0010550978239202164</t>
+          <t>0.009892398472752573 +/- 0.001730294145173839</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.006803193335647351 +/- 0.0015382519823783653</t>
+          <t>-0.0029850746268656357 +/- 0.0012437676409003155</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.0006942034015966714 +/- 0.0010059963031023636</t>
+          <t>-0.0006594932315168167 +/- 0.0007675579447238939</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.0014578271433530188 +/- 0.0011385782344225594</t>
+          <t>0.0022561610551892096 +/- 0.000984815061375289</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.00656022214508849 +/- 0.0011867629987697937</t>
+          <t>-0.01732037486983682 +/- 0.001400932736592187</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0020826102047900143 +/- 0.001480786463568317</t>
+          <t>0.006456091634849037 +/- 0.0017575826311936199</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.007462686567164212 +/- 0.001164214497136295</t>
+          <t>-0.0009371745921554542 +/- 0.0020886756519722703</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.004998264491496008 +/- 0.0011532973082843626</t>
+          <t>-0.0048594238111766665 +/- 0.001379701972533955</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>3.471017007983246e-05 +/- 0.0004771859453268709</t>
+          <t>-0.0032627559875042953 +/- 0.0013814473267707381</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.004720583130857325 +/- 0.0008243208668543976</t>
+          <t>0.0011454356126345377 +/- 0.001280518344026163</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.0014578271433529633 +/- 0.0005332277506330026</t>
+          <t>0.0011801457827143925 +/- 0.0005849461834902178</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0024991322457480368 +/- 0.000979294410251018</t>
+          <t>-0.005171815341895147 +/- 0.001284276292953801</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0061784102742103554 +/- 0.0017888370325199756</t>
+          <t>0.003193335647344697 +/- 0.0018288010929981848</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.009996528982992026 +/- 0.0014709906352250773</t>
+          <t>0.003956959389101034 +/- 0.00180492884415135</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.001284276292953823 +/- 0.0012227639676368244</t>
+          <t>-0.005171815341895147 +/- 0.0010464986762708038</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.0003471017007983246 +/- 0.0005377276426528723</t>
+          <t>-0.0011107254425546387 +/- 0.0006170214798552829</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3.471017007983246e-05 +/- 0.00042369162151105087</t>
+          <t>-0.0004859423811176544 +/- 0.0003181239635512472</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>6.942034015966492e-05 +/- 0.00034008882232323674</t>
+          <t>-0.00197847969455045 +/- 0.000677515491008074</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.007011454356126323 +/- 0.001980609874028075</t>
+          <t>-0.00971884762235332 +/- 0.0025600956493697547</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.012287400208261034 +/- 0.0014985791839585646</t>
+          <t>-0.0013189864630336334 +/- 0.0020405329339394864</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-6.942034015966492e-05 +/- 0.0003738399727271336</t>
+          <t>0.00013884068031934095 +/- 0.0007147261465454305</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.0024991322457480146 +/- 0.0012591709230973418</t>
+          <t>-0.002637972926067289 +/- 0.0009842031849189785</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.006213120444290177 +/- 0.0013393808664751757</t>
+          <t>-0.006768483165567473 +/- 0.001538643544554081</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>-0.0005206525511974869 +/- 0.0005206525511974869</t>
+          <t>0.0005206525511975091 +/- 0.0005650406315897346</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0009371745921555097 +/- 0.0009945538897531809</t>
+          <t>-0.014335300242971161 +/- 0.0011199073797224443</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0013536966331135103 +/- 0.0011765672514181514</t>
+          <t>-0.0023602915654286514 +/- 0.0017479595018416074</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3.471017007982136e-05 +/- 0.0012936234053164864</t>
+          <t>-0.0017007983339118015 +/- 0.0017999156074229989</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.00312391530718501 +/- 0.0013709418714426555</t>
+          <t>0.0023950017355085285 +/- 0.0013029034626257203</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>6.942034015966492e-05 +/- 0.00013884068031932983</t>
+          <t>0.00010413051023949738 +/- 0.000348832892090268</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.004338771259979157 +/- 0.0013010527465457222</t>
+          <t>0.0011107254425547052 +/- 0.0012875555009365849</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0023255813953488636 +/- 0.000982365268870886</t>
+          <t>0.005032974661575884 +/- 0.001355475473083424</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.00013884068031932983 +/- 0.0006051924947643952</t>
+          <t>-0.003366886497743804 +/- 0.0008649729812132906</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.008955223880597019 +/- 0.0014709906352250522</t>
+          <t>0.010656022214508887 +/- 0.0013801385180195</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.00433877125997918 +/- 0.000921618746779012</t>
+          <t>0.002811523776466529 +/- 0.001226698857832148</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.0033668864977438482 +/- 0.0008073379624861566</t>
+          <t>0.003471017007983357 +/- 0.0010976319542409906</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-3.471017007983246e-05 +/- 0.0001869199863635668</t>
+          <t>3.471017007983246e-05 +/- 0.0002883243270710813</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.0004165220409579895 +/- 0.000833044081915979</t>
+          <t>-0.0004859423811176544 +/- 0.0007147261465454164</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.00027768136063865967 +/- 0.0007079513382287606</t>
+          <t>0.00020826102047902806 +/- 0.0012819288658534858</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.00031239153071849213 +/- 0.000394231749101015</t>
+          <t>-0.0002429711905588272 +/- 0.000677515491008074</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.0015619576535925161 +/- 0.0011948569578659233</t>
+          <t>0.00010413051023951957 +/- 0.001590998491685664</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00045123221103782196 +/- 0.000492101592459474</t>
+          <t>0.00027768136063865967 +/- 0.00043352988534524334</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.00555362721277336 +/- 0.0009817518655835648</t>
+          <t>-0.0004165220409579895 +/- 0.0008890141252943667</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0002429711905588272 +/- 0.0010184936307615978</t>
+          <t>-0.0009371745921554764 +/- 0.0010871544438296012</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.00010413051023949738 +/- 0.0006594932315168167</t>
+          <t>4.4408920985006264e-17 +/- 0.0014644236799534207</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.001839639014231198 +/- 0.001130614194717284</t>
+          <t>-0.0021520305449496237 +/- 0.0005553627212773457</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.005275945852134689 +/- 0.0014294522930908685</t>
+          <t>0.0029156542867060375 +/- 0.001584548727596432</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0008330440819160123 +/- 0.0012912929703393433</t>
+          <t>-0.006282540784449797 +/- 0.0013303552861323577</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0032503457814661908 +/- 0.0010163857853872367</t>
+          <t>-0.0022821576763485396 +/- 0.0008910165094553997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00639695712309829 +/- 0.0017237128050642428</t>
+          <t>-0.010926694329184028 +/- 0.0015556323484373377</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.002385892116182631 +/- 0.0006271907727253919</t>
+          <t>-0.0020055325034578075 +/- 0.0009632357038163256</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0010027662517289038 +/- 0.0007801185458283843</t>
+          <t>0.005982019363762081 +/- 0.0012082576216912923</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.003526970954356923 +/- 0.0011958240986024208</t>
+          <t>-0.0025587828492392717 +/- 0.0010396470524462556</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0075034578146611075 +/- 0.00127564776941194</t>
+          <t>0.007226832641770375 +/- 0.001625172890733051</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0006915629322268302 +/- 0.00030927634543565446</t>
+          <t>3.457814661134151e-05 +/- 0.00010373443983402453</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0028354080221300593 +/- 0.0015678816111694231</t>
+          <t>-0.002558782849239283 +/- 0.0016740966026155284</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.015663900414937704 +/- 0.0030067085350384917</t>
+          <t>0.020055325034578075 +/- 0.0024254049677386058</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.013381742738589164 +/- 0.002230491483107895</t>
+          <t>0.013174273858921115 +/- 0.002447243745397017</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0005532503457814641 +/- 0.0008064940380145615</t>
+          <t>0.0058091286307053736 +/- 0.0007052585772604103</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.00048409405255878113 +/- 0.0015632993852638</t>
+          <t>3.457814661134151e-05 +/- 0.0010309855820107552</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.002489626556016644 +/- 0.0016568670194621392</t>
+          <t>0.001763485477178417 +/- 0.001119926330615601</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.016666666666666607 +/- 0.0022183976393285454</t>
+          <t>0.01670124481327795 +/- 0.0018624112046328055</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.005809128630705473 +/- 0.002359435976380643</t>
+          <t>-0.006639004149377648 +/- 0.002734954347619007</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0004495159059474285 +/- 0.0014344722346259907</t>
+          <t>-0.0017289073305670755 +/- 0.0009148517673114042</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.0005532503457814641 +/- 0.0007607192254495132</t>
+          <t>0.001486860304287685 +/- 0.0013126039347235298</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.0025933609958506687 +/- 0.001563681750289809</t>
+          <t>-0.0010027662517289038 +/- 0.0021508051922661036</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.0010373443983402563 +/- 0.00103734439834026</t>
+          <t>0.002109266943291832 +/- 0.0005671237713297603</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.0003112033195020736 +/- 0.0004753709227132597</t>
+          <t>0.0003457814661134151 +/- 0.00021869140111814442</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0012102351313969528 +/- 0.00099318164705014</t>
+          <t>0.005117565698478543 +/- 0.0013374190598764626</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.004598893499308532 +/- 0.0014510466983649523</t>
+          <t>0.0014177040110650019 +/- 0.0011305520556204535</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.00024204702627939056 +/- 0.0007424242930008234</t>
+          <t>0.0010373443983402453 +/- 0.0009016877462244297</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0015905947441217094 +/- 0.0008498067584678052</t>
+          <t>-0.0007607192254495132 +/- 0.0010350366215142264</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0012448132780083054 +/- 0.0008637618255046403</t>
+          <t>0.0013831258644536604 +/- 0.0009278290363069634</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0004495159059474396 +/- 0.0003803596127247566</t>
+          <t>-0.00017289073305670755 +/- 0.00031879475993405444</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0005186721991701116 +/- 0.0016237008135372084</t>
+          <t>0.0003457814661134151 +/- 0.0011363538537451539</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.0015905947441217094 +/- 0.0013048383308515313</t>
+          <t>0.006915629322268302 +/- 0.0017699147845186283</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.0013831258644536938 +/- 0.0013569444585303657</t>
+          <t>-0.009094052558782928 +/- 0.0014007350691928784</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0167358229598894 +/- 0.001716414058919891</t>
+          <t>3.457814661134151e-05 +/- 0.0015575526458582528</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0012102351313969528 +/- 0.000623366403088516</t>
+          <t>3.457814661134151e-05 +/- 0.0004998904666252043</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.001417704011065013 +/- 0.0006642245059577788</t>
+          <t>-0.0004495159059474396 +/- 0.00046520138475358445</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.005636237897648777 +/- 0.0013661650252516143</t>
+          <t>-0.004218533886583708 +/- 0.001754989977932205</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.00020746887966804906 +/- 0.0008637618255046163</t>
+          <t>0.005912863070539398 +/- 0.0012700115955883052</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0006569847856154887 +/- 0.0006992997377647514</t>
+          <t>-0.0009336099585062207 +/- 0.0004387474944830386</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.0007952973720608547 +/- 0.0003112033195020736</t>
+          <t>0.0004149377593360981 +/- 0.0005311995676257664</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0019363762102351245 +/- 0.0010510846579232787</t>
+          <t>0.0075726141078837905 +/- 0.0016470961775677054</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.009024896265560245 +/- 0.0009588813709448132</t>
+          <t>0.0007952973720608547 +/- 0.0012756477694119397</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.00013831258644536604 +/- 0.0005175183107571132</t>
+          <t>-0.001556016597510368 +/- 0.0007294268018578462</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.0008298755186721962 +/- 0.0003850459448706779</t>
+          <t>0.0022130013831258566 +/- 0.001004553184393769</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0038381742738589964 +/- 0.0015028571101038184</t>
+          <t>-0.004183955739972356 +/- 0.0015652102763148632</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0003457814661134151 +/- 0.0008035235158106645</t>
+          <t>0.0017980636237897585 +/- 0.0009755695698247465</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.007123098201936462 +/- 0.0010163857853872074</t>
+          <t>-0.005013831258644574 +/- 0.0015864550134100687</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.003734439834024883 +/- 0.001346329345361806</t>
+          <t>0.0003112033195020736 +/- 0.001222032990807208</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0008298755186722073 +/- 0.0009431660924610013</t>
+          <t>-0.0020055325034578075 +/- 0.0009252481438630433</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.003596127247579606 +/- 0.0013230377918194618</t>
+          <t>-0.0006224066390041472 +/- 0.0008582070294599455</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.00017289073305670755 +/- 0.0003865954317945681</t>
+          <t>-0.0002766251728907321 +/- 0.00013831258644536606</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>-0.002420470262793961 +/- 0.0010601459001906306</t>
+          <t>-0.003250345781466102 +/- 0.0009557589876269159</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.014004149377593422 +/- 0.0013324930060855896</t>
+          <t>-0.0020055325034578075 +/- 0.0008582070294599455</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0007952973720608547 +/- 0.0012375885316855614</t>
+          <t>-0.0035269709543568673 +/- 0.0013284490119155627</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.007468879668049877 +/- 0.0020873289450603757</t>
+          <t>-0.006051175656984864 +/- 0.0010169738015112682</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.0003457814661134151 +/- 0.0005786030612268828</t>
+          <t>0.00013831258644536604 +/- 0.00031691394847550646</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00024204702627939056 +/- 0.0003803596127247566</t>
+          <t>0.0003457814661134151 +/- 0.00043738280223628884</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.0007607192254495132 +/- 0.00020746887966804906</t>
+          <t>-0.001970954356846466 +/- 0.00034750607265286493</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.008298755186722073 +/- 0.0014912765320088347</t>
+          <t>-0.0077455048409405865 +/- 0.002005532503457843</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.005048409405255971 +/- 0.0018504962877260865</t>
+          <t>-0.002455048409405247 +/- 0.0011618463081888924</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-3.457814661134151e-05 +/- 0.00032620958271288277</t>
+          <t>-0.00017289073305670755 +/- 0.00023195725907674086</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.00010373443983402453 +/- 0.0007739636682434063</t>
+          <t>-0.0009336099585062207 +/- 0.0005999084222993572</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.006915629322268413 +/- 0.0018033754924488589</t>
+          <t>-0.0067773167358230356 +/- 0.0016525315553732533</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0004149377593360981 +/- 0.0006146745793440911</t>
+          <t>-0.0005532503457814641 +/- 0.0005175183107571132</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.0056708160442601185 +/- 0.0011998168445987144</t>
+          <t>-0.0071576763485478034 +/- 0.0016074189902032388</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.0036652835408022776 +/- 0.0023102756692241068</t>
+          <t>0.0 +/- 0.0016939763089786786</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.0073651452282158525 +/- 0.0017013713139892809</t>
+          <t>-0.0011410788381742698 +/- 0.0012849864575423223</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.004218533886583775 +/- 0.0007700918897413557</t>
+          <t>6.915629322268302e-05 +/- 0.0009380816020920116</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.00010373443983402453 +/- 0.0003803596127247566</t>
+          <t>-0.00020746887966804906 +/- 0.00022936547651143766</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.0006569847856155109 +/- 0.0013432174688489315</t>
+          <t>0.0006915629322268302 +/- 0.0011363538537451539</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.00024204702627939056 +/- 0.0007583579598707203</t>
+          <t>0.004287690179806347 +/- 0.0006028905869350841</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.0002766251728907321 +/- 0.0004840940525587812</t>
+          <t>-0.0005186721991701226 +/- 0.000678472229265163</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.0005532503457814752 +/- 0.0010045531843937932</t>
+          <t>0.002316735822959881 +/- 0.0007583579598707203</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.0026279391424620215 +/- 0.0015167159197414873</t>
+          <t>0.0036307053941908585 +/- 0.0010402219195360491</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.003596127247579606 +/- 0.0011898098571290182</t>
+          <t>0.00504840940525586 +/- 0.0014273698091666817</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00043738280223628884</t>
+          <t>-0.00020746887966804906 +/- 0.0002766251728907321</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0010719225449515868 +/- 0.0005671237713297603</t>
+          <t>-0.0003457814661134151 +/- 0.0008747656044725777</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6.915629322268302e-05 +/- 0.00048409405255878113</t>
+          <t>0.00013831258644536604 +/- 0.0003850459448706779</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.0008644536652835377 +/- 0.00044416433536186316</t>
+          <t>-0.0003112033195020736 +/- 0.0003927322507469055</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.003941908713693043 +/- 0.0010163857853872072</t>
+          <t>-0.003976486860304318 +/- 0.0013503197918234594</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0003112033195020736 +/- 0.00010373443983402453</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0011065006915629283 +/- 0.0006338278969510129</t>
+          <t>0.0009336099585062207 +/- 0.0004387474944830386</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.00134854771784233 +/- 0.0009588813709448256</t>
+          <t>-0.00024204702627939056 +/- 0.0005367971886673571</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.0010373443983402563 +/- 0.0009278290363069841</t>
+          <t>-0.00048409405255879224 +/- 0.001963356786525383</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0010373443983402453 +/- 0.00040913414820882403</t>
+          <t>0.0005878284923928057 +/- 0.0005367971886673571</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.006535269709543656 +/- 0.0011618463081888922</t>
+          <t>0.0009336099585062207 +/- 0.0011883015406251398</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.00020746887966804906 +/- 0.0006950121453057299</t>
+          <t>0.0006915629322268302 +/- 0.0013569444585303258</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.00280082987551874 +/- 0.000995586448747479</t>
+          <t>0.0021438450899031736 +/- 0.0005949049285644949</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.007074504442925522 +/- 0.0014260181848957546</t>
+          <t>0.0011961722488037841 +/- 0.0010051566076454425</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.006664388243335595 +/- 0.001810056415155891</t>
+          <t>0.004579630895420339 +/- 0.002057404913642175</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.004579630895420394 +/- 0.001243568379949426</t>
+          <t>0.0010594668489404934 +/- 0.0015010383633628028</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.009330143540669833 +/- 0.0009048668690959477</t>
+          <t>-0.002118933697881087 +/- 0.0016376142926467405</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.002187286397812671 +/- 0.0010500541008706108</t>
+          <t>0.0014354066985645454 +/- 0.0010230095384207575</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.009466848940533169 +/- 0.0014664004068984866</t>
+          <t>-0.004306220095693802 +/- 0.001682643010948894</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00044429254955575815 +/- 0.00021883541481315102</t>
+          <t>0.00044429254955565824 +/- 0.00021883541481312847</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.006322624743677352 +/- 0.0013346291312212172</t>
+          <t>0.001503759398496196 +/- 0.0012987012987012794</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.014183185235816853 +/- 0.002856333302583987</t>
+          <t>0.031032125768967835 +/- 0.002947103368053342</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.023239917976760126 +/- 0.0023129083138330436</t>
+          <t>0.03366370471633625 +/- 0.003349456661244466</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.0014695830485303874 +/- 0.001573968412805135</t>
+          <t>0.002563226247436734 +/- 0.0010834495888002356</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0026315789473684626 +/- 0.00206788099896184</t>
+          <t>0.0004442925495556693 +/- 0.0012608247946477602</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0004784688995215669 +/- 0.0016044695275878914</t>
+          <t>-0.0015721120984279135 +/- 0.0020630742683235078</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0038961038961039195 +/- 0.003103092129273032</t>
+          <t>0.002494873547505072 +/- 0.0031362271626147998</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.02354750512645253 +/- 0.0032221973141495592</t>
+          <t>-0.002563226247436823 +/- 0.002113690512107484</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.009501025290499 +/- 0.0015268836571215706</t>
+          <t>-0.0009569377990430783 +/- 0.0015571819206964418</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.004853041695146987 +/- 0.0016518176313868019</t>
+          <t>0.0022898154477101417 +/- 0.001260824794647751</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.0004101161995899272 +/- 0.0017941769990986488</t>
+          <t>0.002358168147641793 +/- 0.0013793872912242367</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.004135338345864692 +/- 0.0007078713320986897</t>
+          <t>0.004237867395762096 +/- 0.0011147987990635915</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00023923444976080565 +/- 0.0003434680663404308</t>
+          <t>0.0002734107997265478 +/- 0.0002979425115202</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.002289815447710164 +/- 0.0022465589103957424</t>
+          <t>0.002563226247436734 +/- 0.0015680204712172885</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.0004784688995215558 +/- 0.0027005804873736572</t>
+          <t>0.0007518796992480814 +/- 0.0006970635015164654</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.001503759398496285 +/- 0.0006338768623031784</t>
+          <t>0.0024265208475734434 +/- 0.0007710536003197744</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.00034176349965827637 +/- 0.001269595052700396</t>
+          <t>-0.0011619958988380642 +/- 0.0012054129930655054</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0010252904989747403 +/- 0.0011335012954051212</t>
+          <t>-0.001161995898838053 +/- 0.0010611192546999466</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.00013670539986333498 +/- 0.0007201403795524815</t>
+          <t>0.0007860560492139124 +/- 0.0003759398496240639</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.005844155844155818 +/- 0.0021037202182518744</t>
+          <t>-0.0005468215994532177 +/- 0.0015526748723992698</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.0030758714969240874 +/- 0.001332439418292414</t>
+          <t>0.005399863294600104 +/- 0.0024965116018796597</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0021531100478468512 +/- 0.0018597085250051735</t>
+          <t>-0.0007518796992481369 +/- 0.0009016340367923966</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.005092276144907737 +/- 0.0027360297415755653</t>
+          <t>-0.002153110047846918 +/- 0.0012515265498018154</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.00020505809979497468 +/- 0.0008537249485165307</t>
+          <t>0.00010252904989744848 +/- 0.00021883541481315102</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0003759398496240296 +/- 0.0004442925495557086</t>
+          <t>-0.0006493506493506773 +/- 0.0003224190407401303</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.004135338345864681 +/- 0.0021960798122238317</t>
+          <t>3.4176349965775454e-05 +/- 0.001074790512202069</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.0003075871496924454 +/- 0.0008839724645507423</t>
+          <t>-0.0005809979494190376 +/- 0.0012792185421881769</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.0025290498974709142 +/- 0.0009928803175894756</t>
+          <t>6.835269993160642e-05 +/- 0.0007298071259078138</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0004784688995215558 +/- 0.0006869361326808616</t>
+          <t>-0.0009911141490089204 +/- 0.0007078713320987041</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.002187286397812749 +/- 0.0010936431989063571</t>
+          <t>0.0021189336978810203 +/- 0.0013394338989928414</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0008202323991797989 +/- 0.001125227452710469</t>
+          <t>0.00010252904989743739 +/- 0.0014584134171805696</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0011961722488038617 +/- 0.0007526560336823236</t>
+          <t>0.00044429254955565824 +/- 0.0003759398496240588</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0029049897470950327 +/- 0.0014276554049354356</t>
+          <t>-0.00023923444976079456 +/- 0.000917684318666963</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.0010594668489405045 +/- 0.0019600069663622257</t>
+          <t>-0.0019480519480519765 +/- 0.001505699984409473</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.002494873547505094 +/- 0.0008918652324470368</t>
+          <t>-0.0035885167464115297 +/- 0.000907444842607771</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.004579630895420339 +/- 0.0017967791425967236</t>
+          <t>0.0007860560492139012 +/- 0.0011544323823687143</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0023581681476418704 +/- 0.0015318479036920771</t>
+          <t>0.003622693096377261 +/- 0.0007361811082890433</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0021531100478469067 +/- 0.0006670957380705054</t>
+          <t>0.00047846889952150027 +/- 0.0005338516524884709</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.011414900888585123 +/- 0.0017033405050413091</t>
+          <t>-0.0023239917976760394 +/- 0.0006264628427827516</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3.417634996586427e-05 +/- 0.0006007654077664526</t>
+          <t>-3.4176349965842065e-05 +/- 0.0003881687180998078</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.005297334244702701 +/- 0.0013346291312212241</t>
+          <t>-0.0007177033492823393 +/- 0.0008839724645507478</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.008475734791524258 +/- 0.002155007897530329</t>
+          <t>-0.0025632262474368115 +/- 0.0020175628356999746</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.001811346548188686 +/- 0.0018970183303319108</t>
+          <t>0.001572112098427847 +/- 0.0013341914761410343</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.005741626794258358 +/- 0.00250118584600573</t>
+          <t>-0.0034859876965140256 +/- 0.0015192146801703977</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.00041011619958990496 +/- 0.0008885850991114139</t>
+          <t>0.0006151742993847798 +/- 0.0004534005181620371</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0004784688995214781 +/- 0.0006151742993848193</t>
+          <t>0.00010252904989744848 +/- 0.00034346806634041416</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0015721120984279247 +/- 0.0003805717267826536</t>
+          <t>-0.0008885850991114386 +/- 0.0003805717267826516</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.002802460697197573 +/- 0.0017074498970330652</t>
+          <t>-0.0025290498974709806 +/- 0.0019163152110562125</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.013738892686261073 +/- 0.0017546818390968366</t>
+          <t>0.009706083390293895 +/- 0.0017639764730777924</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.00034176349965819863 +/- 0.0006484506480181154</t>
+          <t>0.0005126452494873202 +/- 0.0004893308634065818</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.002084757347915278 +/- 0.001217465012341554</t>
+          <t>0.00017088174982907712 +/- 0.001083449588800246</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.004272043745727927 +/- 0.0012991509096888722</t>
+          <t>-0.0011961722488038617 +/- 0.0008679716404101254</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.001469583048530443 +/- 0.0007337973531641647</t>
+          <t>-0.0004101161995899272 +/- 0.0003348584747482144</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.0045454545454545305 +/- 0.0013502902436868431</t>
+          <t>-0.0003075871496924232 +/- 0.0008839724645507458</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-3.417634996579766e-05 +/- 0.001300947799772651</t>
+          <t>0.0010252904989746625 +/- 0.0023727347857429586</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.009432672590567348 +/- 0.0025811630332876635</t>
+          <t>0.0015721120984278358 +/- 0.0017372884521037308</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.01203007518796989 +/- 0.0015795242663419488</t>
+          <t>-0.002016404647983627 +/- 0.0008571384965129223</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.000717703349282317 +/- 0.0002838900841735467</t>
+          <t>-0.0002050580997949858 +/- 0.00016742923737414234</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.002734107997265911 +/- 0.0013147904348373908</t>
+          <t>-0.00034176349965828743 +/- 0.0004585238504784081</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.006801093643198896 +/- 0.0009353337104172301</t>
+          <t>0.004032809295967143 +/- 0.0009016340367924262</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.0029049897470950436 +/- 0.0007830785534784469</t>
+          <t>-0.0011619958988380308 +/- 0.0006697169494964334</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.004989747095010255 +/- 0.001689570347820677</t>
+          <t>0.018933697881066268 +/- 0.0021408694139939764</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.008509911141490068 +/- 0.000984017775043603</t>
+          <t>-0.0025632262474368115 +/- 0.001334629131221217</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.007518796992481191 +/- 0.0013924503614123893</t>
+          <t>-0.000786056049213979 +/- 0.00045979576374140794</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.00017088174982909932 +/- 0.00022926192523918748</t>
+          <t>3.417634996580876e-05 +/- 0.00018404527707226832</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.003075871496924154 +/- 0.0006113651339712286</t>
+          <t>0.001537935748462027 +/- 0.00046484861615637757</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0060150375939849845 +/- 0.001175984315385199</t>
+          <t>0.00027341079972655893 +/- 0.000398561305184225</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.0034176349965824083 +/- 0.0006113651339712286</t>
+          <t>0.0009227614490772251 +/- 0.0006311068117778254</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0018796992481203256 +/- 0.0011463096261960682</t>
+          <t>-0.00013670539986332386 +/- 0.0011559490447906793</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0026999316473001024 +/- 0.0009840177750436174</t>
+          <t>0.002153110047846829 +/- 0.0007800896931314619</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0026657552973342047 +/- 0.0006448380814802959</t>
+          <t>0.00034176349965819863 +/- 0.0005510770846410501</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0069036226930963675 +/- 0.0016798640775727307</t>
+          <t>0.00375939849624054 +/- 0.0010022473204795129</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.002323991797675962 +/- 0.0007912397062741362</t>
+          <t>-0.00020505809979497468 +/- 0.00022670025908105038</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.008612440191387538 +/- 0.001023009538420747</t>
+          <t>0.0015037593984962073 +/- 0.0012435683799494424</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.0013328776486670967 +/- 0.0010747905122020607</t>
+          <t>-0.0025290498974709585 +/- 0.0007823324089035939</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.009090909090909061 +/- 0.0015824794125482195</t>
+          <t>0.0009227614490771918 +/- 0.000837843518259134</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.001507537688442162 +/- 0.0013504619343883667</t>
+          <t>0.0016415410385259733 +/- 0.001221288183152969</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,432 +3111,432 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.0013735343383584953 +/- 0.00098756468830714</t>
+          <t>0.00375209380234508 +/- 0.0012153003113713145</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.008944723618090423 +/- 0.0019130708924983972</t>
+          <t>0.005092127303182592 +/- 0.0013299452757976208</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6.700167504185562e-05 +/- 0.0018214106826221902</t>
+          <t>-0.0015745393634840732 +/- 0.0012539341555921413</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.008542713567839167 +/- 0.002307670365064609</t>
+          <t>0.0043216080402010085 +/- 0.0016713527213757435</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0037855946398659746 +/- 0.0008742370754237813</t>
+          <t>0.0038525963149078856 +/- 0.001162918255122932</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.00023450586264657237 +/- 0.0001535201237841193</t>
+          <t>-0.00026800670016751126 +/- 0.0003608150624545827</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.001809045226130701 +/- 0.0009499126886940168</t>
+          <t>0.002646566164154096 +/- 0.0008534498628379701</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.013668341708542675 +/- 0.0033761132830403074</t>
+          <t>0.004991624790619787 +/- 0.003511840243146964</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.00016750418760471674 +/- 0.0040789935215698354</t>
+          <t>0.009882747068676723 +/- 0.003587093475773691</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.00690117252931326 +/- 0.0013583339988417521</t>
+          <t>-0.004053601340033475 +/- 0.0017111682129476765</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.0015075376884421843 +/- 0.0012102105104313786</t>
+          <t>-0.0010720268006700006 +/- 0.0009332253452049423</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.01661641541038522 +/- 0.0026259186522298596</t>
+          <t>0.0028475711892797517 +/- 0.0011915188773050913</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.00931323283082076 +/- 0.002144053601340025</t>
+          <t>0.006767169179229493 +/- 0.003285132508443905</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.006901172529313193 +/- 0.0021721360237785354</t>
+          <t>0.004824120603015103 +/- 0.0014149890842172907</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0013400335008375453 +/- 0.0011701339495191396</t>
+          <t>0.0004020100502512669 +/- 0.0006140804951364772</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0020100502512562235 +/- 0.0006356337005363745</t>
+          <t>0.002412060301507557 +/- 0.0011777819652426626</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.004087102177554469 +/- 0.001148839410350559</t>
+          <t>-0.0029815745393634518 +/- 0.0008665003119851192</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.0054271356783919256 +/- 0.0012606289931140087</t>
+          <t>0.001976549413735362 +/- 0.001095328825746846</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>0.00010050251256281673 +/- 0.00021451002470462371</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-0.025427135678391943 +/- 0.002596909209552235</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-0.0003685092127303058 +/- 0.0014327239383814516</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.001407035175879423 +/- 0.0008838127945241561</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.006465661641541031 +/- 0.0013236010897915078</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.006030150753768826 +/- 0.0011409974114523396</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-3.350083752093891e-05 +/- 0.0007705192629815948</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-0.005661641541038509 +/- 0.002531253762125771</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.0067671691792295045 +/- 0.002107093493268516</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.00023450586264657237 +/- 0.0009830084255357855</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.005728643216080432 +/- 0.0010210888210471264</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0003015075376884502 +/- 0.00034975901202381326</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-0.0005695142378559614 +/- 0.0003015075376884502</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-0.019497487437185934 +/- 0.0018640439186926037</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.005326633165829109 +/- 0.0010641460753278628</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-0.0050251256281407366 +/- 0.001701631504080434</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.000636515912897806 +/- 0.0012927156704572592</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.0080737018425461 +/- 0.0013437970599753134</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.0008375209380234727 +/- 0.00047965899709469787</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0017755443886096844 +/- 0.001620900556569906</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.009983249581239473 +/- 0.0016870590702866462</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>0.004589614740368475 +/- 0.0010912226113837247</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.006231155778894426 +/- 0.0017160801976369626</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-0.0010050251256281673 +/- 0.0005189927432103879</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0005695142378559503 +/- 0.00033667925028879055</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.0012730318257956675 +/- 0.0010249285454457869</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.001340033500837523 +/- 0.001592611634707497</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.00013400335008375563 +/- 0.0003070402475682386</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>-0.0013735343383584509 +/- 0.0005286342994324467</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>-0.0019095477386934512 +/- 0.0018105955265489734</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0005360134003350225 +/- 0.0007520919370400081</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-0.00020100502512563346 +/- 0.0006898244650577737</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.0026130653266331462 +/- 0.0010139193266613987</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0029145728643216184 +/- 0.0014606518831887104</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0032495812395309854 +/- 0.0013570940770873785</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-0.004489112227805692 +/- 0.0022029188908239375</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.001340033500837523 +/- 0.0017147717108301204</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.0008040201005025227 +/- 0.001050880210476257</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>-0.0020100502512562456 +/- 0.0015205099789494438</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.00020100502512563346 +/- 0.00040201005025126686</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.00013400335008375563 +/- 0.0009732555474930877</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>-0.001976549413735329 +/- 0.0012395309882746927</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.0067671691792295045 +/- 0.0014432602498182863</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.012663316582914575 +/- 0.0015116266898061667</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.00020100502512563346 +/- 0.0007956008098518078</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.0005025125628140836 +/- 0.00016750418760469452</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>6.700167504187781e-05 +/- 0.00013400335008375563</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.0063316582914573205 +/- 0.0012575091711305472</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.009514237855946428 +/- 0.0010401457082921564</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0019765494137352958 +/- 0.0011355746235630485</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-0.0005025125628140947 +/- 0.00206105037390578</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>-0.0007035175879397171 +/- 0.0004089298363729992</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>-0.0008710217755444116 +/- 0.0006391552438304662</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>-0.0013065326633166174 +/- 0.0016713527213757368</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0.0037855946398659746 +/- 0.0007646708348752621</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0.0005025125628140503 +/- 0.0005655592300212228</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.0032830820770519574 +/- 0.000556557712758298</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.0005360134003350337 +/- 0.001683062872640589</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>-0.0006365159128978393 +/- 0.0010428396928826662</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.006968174204355071 +/- 0.0009088549391122877</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>0.006700167504187582 +/- 0.0018102855726775714</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.0011055276381909062 +/- 0.0009119368568720869</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>-0.0026800670016751014 +/- 0.0010161307127707247</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0035510887772194134 +/- 0.0006898244650577737</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>-0.0050251256281407366 +/- 0.0012078898745273038</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0020770519262981236 +/- 0.0013129593261149387</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.015075376884422065 +/- 0.0008863488479278595</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.017085427135678344 +/- 0.0014831453012514979</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>0.00023450586264655015 +/- 0.0005200728541460452</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>-0.0009715242881072284 +/- 0.0006076501556856795</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>6.700167504187781e-05 +/- 0.00020100502512563346</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>0.0013735343383584286 +/- 0.001616740839130799</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.0045561139028475585 +/- 0.001735589125224611</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.001072026800670045 +/- 0.000514649631347994</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.0006365159128978393 +/- 0.0008665003119851192</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>6.700167504186672e-05 +/- 0.0014197400402289678</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>-0.0006365159128978281 +/- 0.0005286342994324713</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-0.0015410385259631454 +/- 0.0009014153465375821</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0.0009045226130653505 +/- 0.0010912226113837695</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-0.003216080402010035 +/- 0.0019887198766708027</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-0.0029145728643215963 +/- 0.001049277036071403</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0.00016750418760469454 +/- 0.00016750418760469452</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>-0.0003685092127303169 +/- 0.0007705192629815761</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>-0.0017755443886096844 +/- 0.0015282404995587344</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>-0.00020100502512562234 +/- 0.00068982446505775</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.01802345058626468 +/- 0.0018640439186926089</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>-0.00020100502512561126 +/- 0.001209746739381422</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>0.00170854271356784 +/- 0.0018130732499477104</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>0.0003350083752093891 +/- 0.0004737733877296926</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.00016750418760469454 +/- 0.0003088624608808419</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>6.700167504187781e-05 +/- 0.0005763702021469248</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>0.0003685092127302947 +/- 0.0007849497161714978</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>0.004154103852596303 +/- 0.0007956008098517909</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>0.006298157453936304 +/- 0.0016329725436454376</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>-3.3500837520950014e-05 +/- 0.0006938799054341049</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-0.0025125628140703848 +/- 0.0009265873826424796</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>0.0018090452261306234 +/- 0.0017420435510887566</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>0.01015075376884419 +/- 0.0018167834992236273</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-0.0005360134003350337 +/- 0.0013990360480951984</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00014982029999998986</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0.005996649916247887 +/- 0.001471369598391806</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.004489112227805658 +/- 0.0014385869717643998</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0.0011055276381908951 +/- 0.0007035175879396823</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0.01896147403685089 +/- 0.0017802787612176284</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>-0.0029145728643216297 +/- 0.0010599190632868364</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>0.017319932998324915 +/- 0.0018413274483968004</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-0.0003015075376884502 +/- 0.00023450586264657237</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.0016080402010049788 +/- 0.0011191486156442365</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>0.000871021775544345 +/- 0.0007370184254606136</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>-0.00023450586264657237 +/- 0.0007035175879397171</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>-0.0014070351758793897 +/- 0.0016398309213427624</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0.001239530988274673 +/- 0.0010704552970633276</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>0.0008375209380234172 +/- 0.001696677690063725</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>-0.00020100502512563346 +/- 0.00016411991576437138</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0010050251256281673 +/- 0.0004968977210784495</t>
+          <t>0.0003350083752093891 +/- 0.0006177249217616839</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0031490787269681463 +/- 0.0010927642499363834</t>
+          <t>-0.0010385259631490729 +/- 0.001574539363484087</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0011390284757119228 +/- 0.0011815874096180142</t>
+          <t>0.003852596314907897 +/- 0.0016833962514440368</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0.0010050251256281117 +/- 0.0016817286965508992</t>
+          <t>0.0006700167504187782 +/- 0.0006177249217616839</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.0036850921273032023 +/- 0.0009235543552489182</t>
+          <t>0.001675041876046901 +/- 0.0012624082868620873</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.006767169179229438 +/- 0.0018580133499312736</t>
+          <t>-0.0006700167504187337 +/- 0.0019476638999997976</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.003986599664991652 +/- 0.001393006558545514</t>
+          <t>-0.00013400335008373343 +/- 0.0010072560387519463</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.003089797232056679 +/- 0.001667439182103458</t>
+          <t>-0.0012552301255230546 +/- 0.0016997419924700441</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.009913099452848429 +/- 0.0018365423389362372</t>
+          <t>-0.008883167042162899 +/- 0.001524650052439913</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.002413904087544283 +/- 0.0017347297043079587</t>
+          <t>-0.008368200836820116 +/- 0.001925751567641006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0015770840038622836 +/- 0.0011283262402933898</t>
+          <t>-0.015159317669777938 +/- 0.0016249637027826648</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.00669456066945604 +/- 0.001732040430907452</t>
+          <t>-0.004956549726424242 +/- 0.0014551212816810233</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.0026392018023817633 +/- 0.0011496988155450024</t>
+          <t>-0.008593498551657563 +/- 0.0018209649385021764</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.0002574831026714075 +/- 0.00031535110946678894</t>
+          <t>-0.0002574831026714186 +/- 0.0005149662053427747</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.0041519150305761475 +/- 0.0014209037692078648</t>
+          <t>-0.010138397167685909 +/- 0.0019109015267199769</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.05838429353073701 +/- 0.00415478327984676</t>
+          <t>0.03221757322175729 +/- 0.0028659456864478417</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.04541358223366589 +/- 0.002511491622130604</t>
+          <t>0.04316060508529125 +/- 0.0035679356981532743</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.005085291277759874 +/- 0.0022055798775683245</t>
+          <t>-9.655616350179308e-05 +/- 0.0008399091310395799</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0025426456388799703 +/- 0.0018345671065336305</t>
+          <t>-0.007853234631477335 +/- 0.0018046792106696085</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.00244608947537821 +/- 0.0020967489507437848</t>
+          <t>-0.007112970711297106 +/- 0.0029514193685206444</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.02832314129385255 +/- 0.0024930694214402417</t>
+          <t>0.02494367557129058 +/- 0.002803086755043838</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.007467009977470218 +/- 0.001371565867567603</t>
+          <t>-0.0009977470228516583 +/- 0.002161219435365226</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.001190859349855189 +/- 0.0014682323434769147</t>
+          <t>-0.011747666559382064 +/- 0.001069891866018326</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.004538139684583209 +/- 0.0013460266280223082</t>
+          <t>-0.007016414547795347 +/- 0.0023422472351027094</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0032185387833922998 +/- 0.0021734075334578656</t>
+          <t>-0.0008368200836820327 +/- 0.002456232253406997</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.00296105568072097 +/- 0.0009305975085163299</t>
+          <t>-0.004602510460251075 +/- 0.0022347415947009865</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>9.655616350173757e-05 +/- 0.0003234591445484651</t>
+          <t>-0.0005471515931767424 +/- 0.0005395254140405692</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.027325394271000947 +/- 0.0021371194465444614</t>
+          <t>0.02404248471194075 +/- 0.0024301566374010644</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.005407145156099147 +/- 0.0009951480420817642</t>
+          <t>-0.0024782748632121375 +/- 0.0008642241121401678</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.00492436433859027 +/- 0.0009660979092245711</t>
+          <t>0.002252977148374591 +/- 0.0018263612435289482</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.001802381718699697 +/- 0.0013594278778205845</t>
+          <t>0.0026070164145477804 +/- 0.001001891368926496</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0007402639201802063 +/- 0.0010776098514826554</t>
+          <t>0.001802381718699686 +/- 0.00080399073040213</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0001287415513357204 +/- 0.00045969928732172185</t>
+          <t>0.0007402639201801953 +/- 0.0005199708536016431</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.009655616350176999 +/- 0.001589840879977904</t>
+          <t>-0.0008690054715159712 +/- 0.0019947152149785916</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.004151915030576159 +/- 0.0018847011228783298</t>
+          <t>-0.005117476665593856 +/- 0.0016249637027826917</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.0008046346958481054 +/- 0.0015317674971729416</t>
+          <t>-0.0028001287415513666 +/- 0.0019043852195026645</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.0011586739620212728 +/- 0.0016798182620791518</t>
+          <t>-0.002993241068554908 +/- 0.00173950036908551</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0001287415513357315 +/- 0.0008779003345340128</t>
+          <t>0.001158673962021206 +/- 0.00048170677653992355</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.000643707756678491 +/- 0.0005385645487827966</t>
+          <t>0.0003862246540070613 +/- 0.00047302666420016945</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.006758931445123883 +/- 0.0021876595388434414</t>
+          <t>-0.013196009011908627 +/- 0.0016661962157122365</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.002413904087544283 +/- 0.00093559329602502</t>
+          <t>-0.0010943031863534403 +/- 0.0030472611209641535</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0019954940457032723 +/- 0.0007724493080141494</t>
+          <t>-0.00035403926617320056 +/- 0.000767741257925767</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.0001287415513357204 +/- 0.0005611714121069572</t>
+          <t>0.001029932410685519 +/- 0.0007724493080141577</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.00469906662375279 +/- 0.0011260286890592687</t>
+          <t>0.0009333762471837592 +/- 0.0013839716768587068</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.003508207273897679 +/- 0.0015797091975292038</t>
+          <t>0.0008690054715158934 +/- 0.0014397341001831496</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.655616350181528e-05 +/- 0.0005395254140405606</t>
+          <t>-0.0017058255551979818 +/- 0.0007486130254015389</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0015127132281943733 +/- 0.0008148689347391156</t>
+          <t>0.004602510460251019 +/- 0.0016540283434218798</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0016414547795300717 +/- 0.0016875090735652741</t>
+          <t>-0.0007080785323463568 +/- 0.0017018737130868827</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0003540392661731229 +/- 0.0009040599874598119</t>
+          <t>0.004763437399420633 +/- 0.0007589202524976967</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.003733504988735148 +/- 0.0020467477432358624</t>
+          <t>-0.0047956227872546385 +/- 0.001442609258513992</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.002156420984872842 +/- 0.001279748654784112</t>
+          <t>-0.007499195365304201 +/- 0.0013352087874278305</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.002767943353717417 +/- 0.0013363720303847242</t>
+          <t>-0.011071773414869679 +/- 0.002226149528907693</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.003636948825233366 +/- 0.0015304143454095774</t>
+          <t>-0.008786610878661106 +/- 0.0019260205085776887</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.000708078532346279 +/- 0.0003753428963531122</t>
+          <t>0.0016736401673639878 +/- 0.0005149662053427831</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.005342774380431259 +/- 0.0018611950170326459</t>
+          <t>-0.0021242355970389703 +/- 0.0008167735784003351</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.003282909559060232 +/- 0.0017908500474082406</t>
+          <t>-0.008336015448986189 +/- 0.0015058497026442708</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.010041841004184116 +/- 0.002049782211534072</t>
+          <t>-0.005117476665593845 +/- 0.0016185762421216878</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.0002252977148374913 +/- 0.0012217736012939953</t>
+          <t>-0.009623430962343115 +/- 0.002161219435365247</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.00016092693916958112 +/- 0.0005433518833644688</t>
+          <t>0.002349533311876373 +/- 0.000802055731855631</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0009333762471837592 +/- 0.000767741257925738</t>
+          <t>0.0008046346958480388 +/- 0.000737459880102329</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0007402639201801953 +/- 0.000433010107726882</t>
+          <t>-5.551115123125783e-17 +/- 0.0005385645487828098</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.010395880270357283 +/- 0.0019260205085776816</t>
+          <t>-0.012487930479562304 +/- 0.001379097861965136</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.0013839716768587306 +/- 0.0017215422105331679</t>
+          <t>-0.013099452848406856 +/- 0.0016911882401570077</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.0020920502092049986 +/- 0.0007513754444756282</t>
+          <t>0.0005793369810105809 +/- 0.0005899679040818643</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0016414547795301272 +/- 0.0013537007302744054</t>
+          <t>-0.003765690376569064 +/- 0.001187374750286261</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.0001287415513357204 +/- 0.0012890237782105358</t>
+          <t>-0.007853234631477357 +/- 0.0010096161661640303</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0015127132281943733 +/- 0.00047847018819824463</t>
+          <t>0.0007724493080141226 +/- 0.0008167735784003623</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0020276794335372106 +/- 0.0015770840038622457</t>
+          <t>0.0009977470228515807 +/- 0.0019863886867343868</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.007660122304473771 +/- 0.000772449308014155</t>
+          <t>-0.007788863855809502 +/- 0.002279489051770313</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.00019311232700356396 +/- 0.0011886826721995017</t>
+          <t>-0.005857740585774085 +/- 0.001430711990401864</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.0019311232700354175 +/- 0.0011514994412615443</t>
+          <t>0.006823302220791727 +/- 0.0017439610150169615</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-3.218538783396063e-05 +/- 0.00030363634155315574</t>
+          <t>9.655616350171537e-05 +/- 0.00045630662628767446</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.0035082072738976122 +/- 0.0012251603676005215</t>
+          <t>0.0009977470228515917 +/- 0.0012166757754384163</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0030254264563888246 +/- 0.0014408129569101593</t>
+          <t>-0.006758931445123939 +/- 0.0025708047052096315</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0026070164145477913 +/- 0.0009487868022519287</t>
+          <t>-0.00045059542967496036 +/- 0.0011799358081637343</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.01593176697779205 +/- 0.0013053942575264323</t>
+          <t>0.006404892178950727 +/- 0.002580658034811862</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>3.218538783390512e-05 +/- 0.0011908593498551588</t>
+          <t>-0.002735757965883523 +/- 0.0019324638625398322</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.0007080785323463456 +/- 0.0011586739620212264</t>
+          <t>-0.004087544254908304 +/- 0.0021448609052521633</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.00022529771483750238 +/- 0.00025137591489883673</t>
+          <t>0.0007402639201802175 +/- 0.0004784701881982275</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.0007080785323463678 +/- 0.0007589202524976713</t>
+          <t>0.00383006115223683 +/- 0.0008808453288319276</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0007080785323463456 +/- 0.0006872918089495384</t>
+          <t>0.0028644995172191546 +/- 0.0010324438321432498</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.0002574831026714186 +/- 0.0007724493080141494</t>
+          <t>-0.0007080785323463568 +/- 0.0007589202524976958</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.0020276794335371993 +/- 0.0012878177678624211</t>
+          <t>0.0031541680077244783 +/- 0.0012025453294025924</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.000643707756678491 +/- 0.0004773864491210656</t>
+          <t>0.0014161570646925915 +/- 0.0007080785323463134</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0019633086578693002 +/- 0.0018232390136168086</t>
+          <t>-0.0036369488252333882 +/- 0.0019313914629774537</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.003572578049565489 +/- 0.0018289118307274399</t>
+          <t>-0.00045059542967496036 +/- 0.0014551212816810216</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.004473768908915399 +/- 0.0007811175474420051</t>
+          <t>-0.0009655616350177532 +/- 0.0008515453205872548</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.002510460251045998 +/- 0.0016711625343736308</t>
+          <t>0.004731252011586695 +/- 0.0016665070442226846</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-6.437077566788796e-05 +/- 0.0015885371972002627</t>
+          <t>-0.005471515931767012 +/- 0.0019892548619713695</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.0013517862890248034 +/- 0.0010943031863533906</t>
+          <t>0.0020598648213710825 +/- 0.0009011908593498565</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0002756719503789973 +/- 0.0012405237767056914</t>
+          <t>0.005306685044796755 +/- 0.0009648518263266665</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0077877325982080746 +/- 0.0022129006696074752</t>
+          <t>-0.0014128187456926011 +/- 0.0019089784954465126</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002067539627842796 +/- 0.0014700709171400093</t>
+          <t>0.005099931082012454 +/- 0.0017557187047356254</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.000447966919365983 +/- 0.000912350261535037</t>
+          <t>0.0012749827705031192 +/- 0.0007070394393068049</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0021709166092349296 +/- 0.001045760916987852</t>
+          <t>-0.0001722949689868858 +/- 0.0013279013692624028</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.445899379732609e-05 +/- 0.0023846520023150775</t>
+          <t>0.004789800137836031 +/- 0.001780233129302485</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00010337698139211149 +/- 0.0001579109474484641</t>
+          <t>-6.89179875947632e-05 +/- 0.0001378359751895264</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0002756719503789862 +/- 0.0011197847559801133</t>
+          <t>0.00172294968986908 +/- 0.001378359751895264</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.009303928325292843 +/- 0.0025462375192158706</t>
+          <t>0.018435561681598944 +/- 0.003759822060716472</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.010854583046174981 +/- 0.00168989660030867</t>
+          <t>0.007133011716057935 +/- 0.003771804080213925</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.006685044796691908 +/- 0.0011240183618401165</t>
+          <t>0.005168849069607217 +/- 0.0016740121022041409</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.00368711233631972 +/- 0.0012333239261318768</t>
+          <t>0.006064782908339106 +/- 0.0017174274010168132</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.005651274982770471 +/- 0.0011655089266221917</t>
+          <t>0.0043073742246726885 +/- 0.0017654980644313616</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.010303239145416887 +/- 0.001529063248265597</t>
+          <t>0.009648518263266747 +/- 0.002162971030527263</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.007098552722260454 +/- 0.0014390498289331987</t>
+          <t>0.0055478980013784155 +/- 0.001684265942088194</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.00454858718125426 +/- 0.0012114676658337143</t>
+          <t>-0.00034458993797379376 +/- 0.000986755414422884</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.0001378359751894709 +/- 0.00108093639843954</t>
+          <t>0.00172294968986908 +/- 0.0014373985950802551</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.003101309441764233 +/- 0.0010896890627734056</t>
+          <t>0.006443831840110326 +/- 0.000830597573617748</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.0030323914541694696 +/- 0.0015624788488979727</t>
+          <t>0.0022053756030324225 +/- 0.0018505474268914873</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.00020675396278428958 +/- 0.00022857510615819756</t>
+          <t>-0.0001378359751895264 +/- 0.00016881390370663077</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.003687112336319842 +/- 0.0018431535658602776</t>
+          <t>-0.00010337698139211149 +/- 0.001875088609291893</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.008787043418332119 +/- 0.001632716435628121</t>
+          <t>0.004514128187456989 +/- 0.0011882108648908964</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.0007580978635424174 +/- 0.0013505112296530195</t>
+          <t>0.0028945554789800544 +/- 0.0011240183618401324</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.000689179875947643 +/- 0.0008007546546259225</t>
+          <t>0.0023776705720193305 +/- 0.0012656352634188295</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0005513439007580389 +/- 0.0007260960546417811</t>
+          <t>-0.0009303928325292588 +/- 0.0013614573580384608</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0002412129565816712 +/- 0.00026913334513806907</t>
+          <t>-0.00010337698139213369 +/- 0.0008014957511793829</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.006891798759476287 +/- 0.0012707849010741249</t>
+          <t>0.002756719503790528 +/- 0.0011112691589660456</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.004824259131633313 +/- 0.0012707849010741578</t>
+          <t>0.0018263266712612246 +/- 0.0009873569112263684</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.004203997243280444 +/- 0.001054242490749729</t>
+          <t>0.010647829083390802 +/- 0.0009921557580212384</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.006616126809097145 +/- 0.0015083438062191013</t>
+          <t>0.00792556857339768 +/- 0.0011634695393613983</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.00024121295658160457 +/- 0.0006363261651488037</t>
+          <t>-0.0011371467953135484 +/- 0.000409177880325182</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.0001722949689869302 +/- 0.0004426337897541111</t>
+          <t>-3.44589937973816e-05 +/- 0.000521459198842928</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.001654031702274228 +/- 0.0011091300440682858</t>
+          <t>0.0035492763611303046 +/- 0.001122432630937461</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.000620261888352891 +/- 0.0008270158511371325</t>
+          <t>0.004272915230875318 +/- 0.0012443466633541035</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.001033769813921448 +/- 0.00030821061026875546</t>
+          <t>-6.89179875947632e-05 +/- 0.0006857253184745927</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.00017229496898685248 +/- 0.0006018004547405936</t>
+          <t>0.0011371467953135927 +/- 0.0007398659735900823</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0007061992257725149</t>
+          <t>0.001895244658855999 +/- 0.0018700156514424788</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.003445899379738049 +/- 0.0011112691589660459</t>
+          <t>0.008097863542384575 +/- 0.0016543906111864616</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0006202618883527911 +/- 0.0005724758003389157</t>
+          <t>0.002756719503790528 +/- 0.0005968472803476574</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0007580978635422953 +/- 0.0003711347213738284</t>
+          <t>0.000344589937973816 +/- 0.0008007546546259415</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.00020675396278424518 +/- 0.0014140788786135621</t>
+          <t>0.0011371467953135927 +/- 0.0011118032946176365</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0023776705720193305 +/- 0.0011475414062954476</t>
+          <t>-0.0006202618883528243 +/- 0.001119784755980118</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.0022053756030324333 +/- 0.0017312000947044145</t>
+          <t>-0.006788421778084053 +/- 0.0012805585235053</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>3.4458993797314984e-05 +/- 0.0011475414062953962</t>
+          <t>-0.002929014472777336 +/- 0.0008475791782390527</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.00010337698139210039 +/- 0.0010682288077187836</t>
+          <t>0.0009993108201240663 +/- 0.0012371690607178836</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0012749827705031303 +/- 0.0012524315537826407</t>
+          <t>0.0007236388697450247 +/- 0.0016913013358798136</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0015161957270846793 +/- 0.0004921728758472053</t>
+          <t>-0.0001378359751895264 +/- 0.00022857510615819756</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0016195727084768242 +/- 0.0007865411585467599</t>
+          <t>-0.002136457615437548 +/- 0.0006501709946283071</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.0054100620261889 +/- 0.0017641524102233312</t>
+          <t>-0.003618194348724957 +/- 0.0015959388252115194</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.007891109579600309 +/- 0.0011781751204189078</t>
+          <t>2.2204460492503132e-17 +/- 0.001541053051343745</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.0034803583735355413 +/- 0.0014493274186639135</t>
+          <t>-0.004203997243280444 +/- 0.0011917034090827585</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0003790489317712309 +/- 0.0006250295364306061</t>
+          <t>-0.001240523776705682 +/- 0.0006391191244310975</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.0007925568573397768 +/- 0.0004372356147639455</t>
+          <t>0.0007925568573397768 +/- 0.0010682288077188296</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0011716057891108633 +/- 0.000351414163583243</t>
+          <t>-0.0005513439007581056 +/- 0.000383719115288084</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.004203997243280555 +/- 0.0014925160460170929</t>
+          <t>-0.002963473466574729 +/- 0.001362764985064439</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.005858028945554872 +/- 0.0010105360646874835</t>
+          <t>-0.002825637491385191 +/- 0.001323871310289356</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,147 +4286,147 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0016195727084769352 +/- 0.0007236388697450136</t>
+          <t>0.001378359751895264 +/- 0.0006353924505370789</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.001378359751895275 +/- 0.0012328424410750001</t>
+          <t>-0.009338387319090258 +/- 0.0019151885915355033</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.007029634734665802 +/- 0.0017035433624132481</t>
+          <t>-0.00282563749138518 +/- 0.0012016261732710502</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.0001722949689868636 +/- 0.0006212183451867315</t>
+          <t>0.00041350792556857916 +/- 0.0007195249144666227</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.0003790489317711532 +/- 0.0013026228925868612</t>
+          <t>-0.002515506547208757 +/- 0.000987356911226344</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.005444521019986282 +/- 0.0019358472646710096</t>
+          <t>-0.005961405926946906 +/- 0.0015103106134260118</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.0038938662991040095 +/- 0.0004635983475904169</t>
+          <t>0.0004135079255685903 +/- 0.0011407956827875106</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.0007580978635423174 +/- 0.0012309146174701163</t>
+          <t>-0.007718814610613367 +/- 0.0012911780837488254</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.0003101309441764344 +/- 0.00010337698139214479</t>
+          <t>-0.000344589937973816 +/- 0.00015410530513437773</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.001378359751895275 +/- 0.0011532185065941734</t>
+          <t>-0.0023776705720192303 +/- 0.0010502929465284717</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.00048242591316326465 +/- 0.0012443466633540658</t>
+          <t>-0.0023432115782218597 +/- 0.0011614265710787385</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.445899379733719e-05 +/- 0.0008503764768609612</t>
+          <t>-0.0004824259131633313 +/- 0.0007422694427476785</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.004617505168849134 +/- 0.0016323527611753518</t>
+          <t>-0.007960027567195016 +/- 0.0013026228925868783</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.0014472777394900493 +/- 0.0012500590728612543</t>
+          <t>0.0008959338387319216 +/- 0.001234767254801459</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-0.005203308063404621 +/- 0.0009555771622234487</t>
+          <t>-0.0039972432804961655 +/- 0.0013800816260855079</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.00015410530513435293</t>
+          <t>0.000516884906960724 +/- 0.00046869298789578334</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.0008959338387319216 +/- 0.0007580978635423951</t>
+          <t>6.89179875947632e-05 +/- 0.00030040654331776255</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.0016195727084769352 +/- 0.0007070394393068049</t>
+          <t>-0.0018607856650585063 +/- 0.0004412904367631038</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>6.891798759474099e-05 +/- 0.00013783597518948198</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0001378359751894709 +/- 0.000709554110336769</t>
+          <t>0.0002412129565816712 +/- 0.0007712966673190801</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.002653342522398383 +/- 0.0010227995919818082</t>
+          <t>-0.001240523776705682 +/- 0.002108484981499411</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000172294968986908 +/- 0.000172294968986908</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.00024121295658160457 +/- 0.0007398659735900317</t>
+          <t>-0.0011716057891109411 +/- 0.0006391191244310928</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.000206753962784334 +/- 0.0012251129451847597</t>
+          <t>-0.002170916609234963 +/- 0.0016092755932233618</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.0002756719503790972 +/- 0.0010081832417868667</t>
+          <t>-0.0008614748449344845 +/- 0.001625427486570722</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.000275671950379075 +/- 0.0007518064861912736</t>
+          <t>-0.0003790489317711754 +/- 0.0007462580230085116</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.005341144038594037 +/- 0.0015809882490633526</t>
+          <t>-0.0015506547208821054 +/- 0.0016757844818452976</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.007822191592005544 +/- 0.0015181523619510887</t>
+          <t>-0.013576843556168127 +/- 0.0016468370979116041</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.0015851137146794647 +/- 0.0009143004246327516</t>
+          <t>0.002136457615437659 +/- 0.0009843457516944107</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.005353037766830904 +/- 0.0010595905290575992</t>
+          <t>9.852216748770237e-05 +/- 0.001687706424634431</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.005385878489326779 +/- 0.0017818929348112327</t>
+          <t>-0.013399014778325103 +/- 0.0018623903945822868</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.012019704433497536 +/- 0.001732795528180361</t>
+          <t>-0.0031855500821017847 +/- 0.002832881154443968</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.00285714285714288 +/- 0.0015124570035690607</t>
+          <t>-0.006732348111658437 +/- 0.0013400463555404453</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.006272577996715933 +/- 0.001950915827951276</t>
+          <t>0.007619047619047636 +/- 0.0013604147899643926</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0020032840722496005 +/- 0.0013812637664901914</t>
+          <t>-0.0015763546798029271 +/- 0.001908156196562763</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0010180623973727431 +/- 0.0006958824335112157</t>
+          <t>-0.00016420361247946325 +/- 0.0004218467185111635</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.0021346469622331664 +/- 0.0009658746252776823</t>
+          <t>0.0003284072249589709 +/- 0.0021635033289984255</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.009359605911330027 +/- 0.004452916179174377</t>
+          <t>-0.009458128078817718 +/- 0.0038095238095238074</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.014844006568144474 +/- 0.003857352212814732</t>
+          <t>-0.003513957307060722 +/- 0.0029412162801388895</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.000886699507389166 +/- 0.0010697206880067188</t>
+          <t>-0.007027914614121477 +/- 0.0019047619047619106</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.005221674876847304 +/- 0.0021607598226070306</t>
+          <t>-0.0004926108374383786 +/- 0.0019989724523524753</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.011625615763546792 +/- 0.0022088895528144725</t>
+          <t>0.015303776683087033 +/- 0.00310583656289967</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.0188177339901478 +/- 0.0027478482293279375</t>
+          <t>0.02748768472906408 +/- 0.00327766205265517</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.034515599343185564 +/- 0.002629104441330118</t>
+          <t>0.04620689655172418 +/- 0.003177414152889794</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.002824302134646983 +/- 0.001050903119868641</t>
+          <t>0.005385878489326768 +/- 0.001960566378535217</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.004039408866995086 +/- 0.001694084778525951</t>
+          <t>0.005648604269293933 +/- 0.0020340049349362064</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.0006896551724137945 +/- 0.002528735632183913</t>
+          <t>0.004006568144499201 +/- 0.001303739457555294</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.0005582922824302172 +/- 0.0016357844867536553</t>
+          <t>0.00801313628899838 +/- 0.0016367731749592383</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0003885766688407231</t>
+          <t>0.0004926108374384453 +/- 0.00036717043965513743</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.0015435139573070633 +/- 0.001731861658250922</t>
+          <t>-0.005188834154351363 +/- 0.0027780999648678623</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0008210180623973717 +/- 0.0018417175557057435</t>
+          <t>-0.0011494252873562982 +/- 0.0016502258819574404</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.005418719211822698 +/- 0.0013797012504170674</t>
+          <t>0.0016091954022988797 +/- 0.0014572550234702145</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.002397372742200332 +/- 0.0017256229432406815</t>
+          <t>0.0010837438423645595 +/- 0.001193614571125528</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0031198686371100236 +/- 0.0016038246892709088</t>
+          <t>0.00042692939244665107 +/- 0.0016748768472906281</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0007224958949096805 +/- 0.0005455910583197316</t>
+          <t>0.00016420361247948545 +/- 0.001041107880732163</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.01021346469622333 +/- 0.002037448587093092</t>
+          <t>0.0020032840722496005 +/- 0.0020793650073269976</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.00545155993431855 +/- 0.001982448377377549</t>
+          <t>-0.020394088669950728 +/- 0.0021102560034702506</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.0006568144499179085 +/- 0.0017190479249001487</t>
+          <t>-0.004794745484400631 +/- 0.0013793103448275763</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.010574712643678152 +/- 0.001015410498111038</t>
+          <t>-0.004433497536945774 +/- 0.001739318578241751</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.00016420361247948545 +/- 0.0003365172665339993</t>
+          <t>-0.00013136288998357725 +/- 0.0004205664523765472</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.00013136288998358837 +/- 0.00044547323370283865</t>
+          <t>-9.852216748766907e-05 +/- 0.00048821243833558264</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.005123152709359591 +/- 0.0011489560383931602</t>
+          <t>0.001313628899835817 +/- 0.0019036291292202836</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0008538587848932689 +/- 0.002615738292510995</t>
+          <t>-0.010738916256157627 +/- 0.001109316634092255</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.00036124794745482356 +/- 0.0006958824335112304</t>
+          <t>0.00042692939244663996 +/- 0.0007496034292619486</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0007553366174055775 +/- 0.0010390339585915733</t>
+          <t>-0.001018062397372721 +/- 0.0009224677770238527</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.006371100164203625 +/- 0.0027089117408606</t>
+          <t>3.28407224959304e-05 +/- 0.0017773476686679657</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.00036124794745483467 +/- 0.001357637215671248</t>
+          <t>-0.0070607553366173635 +/- 0.0019498098665086875</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0014121510673234749 +/- 0.000416702053873555</t>
+          <t>-0.0004926108374384008 +/- 0.0004702075882849263</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.004991789819376036 +/- 0.0013283250191235803</t>
+          <t>0.0021346469622332 +/- 0.0015629561949807363</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0024958949096880235 +/- 0.002431987991011319</t>
+          <t>0.0016420361247947769 +/- 0.001439008361261507</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.008144499178981945 +/- 0.002142463898890002</t>
+          <t>0.00036124794745487907 +/- 0.0012061982050710568</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.008932676518883409 +/- 0.002001937688555417</t>
+          <t>-0.008866995073891581 +/- 0.0017377676919964555</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.010837438423645328 +/- 0.0023590522162322386</t>
+          <t>-0.004269293924466322 +/- 0.0017562879418221249</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.00266009852216752 +/- 0.000990135529174491</t>
+          <t>-0.004532019704433477 +/- 0.0012444857354020618</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.0005582922824302172 +/- 0.0007202532742023496</t>
+          <t>-0.006305418719211808 +/- 0.0015459576086620365</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0015763546798029493 +/- 0.0005045087519125857</t>
+          <t>-9.852216748768017e-05 +/- 0.0003899619733017478</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0038423645320197265 +/- 0.0007202532742023375</t>
+          <t>0.000328407224958982 +/- 0.0014832958674070539</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.005024630541871899 +/- 0.0022896838113042337</t>
+          <t>-0.020722495894909675 +/- 0.001983807988248148</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.024302134646962226 +/- 0.0021734505231887553</t>
+          <t>-0.0160591133004926 +/- 0.0023103162347404334</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.01599343185550082 +/- 0.0025651526548674773</t>
+          <t>-0.020821018062397344 +/- 0.00286374113058677</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-0.00042692939244662884 +/- 0.0006064428674095012</t>
+          <t>0.002791461412151086 +/- 0.0008963772784207596</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.001970443349753703 +/- 0.0005874727034482411</t>
+          <t>0.0007881773399015079 +/- 0.0007372723914825435</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.00026272577996717673 +/- 0.0003217720515971547</t>
+          <t>0.000361247947454868 +/- 0.0003098187563894</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.023973727422003276 +/- 0.0027120949519950934</t>
+          <t>-0.04085385878489324 +/- 0.0033400806923063716</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.021477832512315255 +/- 0.0009764248766711676</t>
+          <t>-0.0034154351395730307 +/- 0.0018414247315436804</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.003152709359605932 +/- 0.0005911330049261118</t>
+          <t>0.0029556650246305495 +/- 0.0006401835366048607</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.0020032840722496005 +/- 0.0012757257536653859</t>
+          <t>0.003875205254515612 +/- 0.0008282115082376637</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.022200328407224967 +/- 0.0022040015416174173</t>
+          <t>-0.019343185550082076 +/- 0.002324278788731767</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.0006568144499178863 +/- 0.0004871066329783561</t>
+          <t>-0.00019704433497534922 +/- 0.0007517584986705912</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.005287356321839109 +/- 0.0011324098291997885</t>
+          <t>-0.0005911330049260921 +/- 0.0009495456351264976</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.030574712643678136 +/- 0.0020845452968877866</t>
+          <t>-0.012939244663382598 +/- 0.0010405897877014704</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.00016420361247947434 +/- 0.0012483794948274626</t>
+          <t>0.002627257799671612 +/- 0.0016681018192709542</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.005418719211822654 +/- 0.0011015113189654189</t>
+          <t>-0.0015106732348111219 +/- 0.0008203609850112708</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0007224958949097026 +/- 0.000435681417452253</t>
+          <t>-0.0002955665024630405 +/- 0.000538627897105311</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.005353037766830893 +/- 0.001875374914321078</t>
+          <t>6.568144499181638e-05 +/- 0.001360414789964384</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.0030541871921182296 +/- 0.0005697652404892458</t>
+          <t>-0.0022660098522167328 +/- 0.0014044929248172738</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-0.00016420361247947434 +/- 0.0008842635151288215</t>
+          <t>-0.002430213464696196 +/- 0.001230541477516924</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.007126436781609213 +/- 0.002256470723980544</t>
+          <t>0.004630541871921201 +/- 0.0016774506126925536</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.00390804597701151 +/- 0.0016118740481849423</t>
+          <t>-0.005977011494252837 +/- 0.0012870882063885335</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.007323481116584573 +/- 0.0014836593757736008</t>
+          <t>0.005517241379310356 +/- 0.001278681269880558</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.00013136288998358837 +/- 0.00033491096969412963</t>
+          <t>0.00026272577996717673 +/- 0.0002862987811849565</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-0.0007224958949097138 +/- 0.00060198038685791</t>
+          <t>-0.0030541871921181962 +/- 0.001138109914690545</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.001477832512315269 +/- 0.0008595239624500584</t>
+          <t>-0.00019704433497534922 +/- 0.0005534416928194612</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.0021674876847290747 +/- 0.0010812530465126146</t>
+          <t>-0.0022660098522167328 +/- 0.001284152039147272</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.004564860426929396 +/- 0.001419767902871412</t>
+          <t>0.00013136288998358837 +/- 0.0017575156860767896</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>6.568144499179418e-05 +/- 0.00013136288998358837</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0014121510673234861 +/- 0.0005697652404892458</t>
+          <t>0.00039408866995075396 +/- 0.0005650131538287634</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.0021018062397372694 +/- 0.001130026307657483</t>
+          <t>-0.0019047619047618757 +/- 0.0013604147899643937</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.004860426929392448 +/- 0.0013683196489983258</t>
+          <t>0.003251231527093601 +/- 0.0019118265455274966</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0011822660098522175 +/- 0.0008713628349045304</t>
+          <t>-0.0037110016420360825 +/- 0.0013303533070955127</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0007224958949097026 +/- 0.0009830298553100637</t>
+          <t>0.003284072249589509 +/- 0.0007488836946463825</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.005320197044334984 +/- 0.0012786812698805884</t>
+          <t>-0.003251231527093568 +/- 0.0011131987689115442</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.00482758620689655 +/- 0.0015957347275213623</t>
+          <t>-0.001444991789819361 +/- 0.0005725975623698748</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.00024432809773126116 +/- 0.0008973794158591455</t>
+          <t>-0.0015357766143107021 +/- 0.0012985043795977849</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.0002443280977311835 +/- 0.0014976221956666655</t>
+          <t>-0.006980802792321161 +/- 0.001489056126192079</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0021989528795811285 +/- 0.0016375154074331423</t>
+          <t>-0.0011867364746946385 +/- 0.00171846891798831</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00017452006980808176 +/- 0.001128323202460359</t>
+          <t>-0.0018848167539267547 +/- 0.001440821461818505</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.000523560209424101 +/- 0.0012315726886127374</t>
+          <t>-0.004921465968586436 +/- 0.0014173780456716884</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0014659685863874562 +/- 0.001722717302513522</t>
+          <t>0.004118673647469406 +/- 0.002587609492893618</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0002443280977312834 +/- 0.00015995028603688207</t>
+          <t>-3.3306690738754695e-17 +/- 0.00027036532957818517</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0002792321116928731 +/- 0.001628189010777051</t>
+          <t>0.004397905759162268 +/- 0.0013891622158556545</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.03563699825479934 +/- 0.0036086429371253934</t>
+          <t>0.03699825479930187 +/- 0.0022620386381877475</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.030750436300174554 +/- 0.00378656272278005</t>
+          <t>0.04062827225130886 +/- 0.0033486031288548503</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0050261780104712385 +/- 0.000964766140389884</t>
+          <t>0.0028970331588132115 +/- 0.0011995001938875796</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.001989528795811479 +/- 0.0010592663808372575</t>
+          <t>-0.005759162303664966 +/- 0.0012015298064962454</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0006980802792320828 +/- 0.002310002388519981</t>
+          <t>-0.0015008726003490902 +/- 0.001637515407433146</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.015183246073298462 +/- 0.002247178862522849</t>
+          <t>0.010715532286212859 +/- 0.002304986664027789</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.003839441535776633 +/- 0.0010116144325437572</t>
+          <t>0.004677137870855097 +/- 0.0011059671565622714</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0005235602094241232 +/- 0.0012116268731385414</t>
+          <t>-0.0030366492146597255 +/- 0.0009372231470923219</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.0006282722513089145 +/- 0.0013679523868946246</t>
+          <t>-0.0008726003490401868 +/- 0.001815344310498541</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.006910994764397949 +/- 0.0015671863400100305</t>
+          <t>0.003979057591622992 +/- 0.0015230313598095062</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0006282722513089145 +/- 0.0012070936450813811</t>
+          <t>-0.0017452006980803291 +/- 0.0017382058775551512</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0006282722513088812 +/- 0.0004886561954624764</t>
+          <t>-3.490401396162301e-05 +/- 0.0001879638676137812</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.014869109947644 +/- 0.0009520545687250242</t>
+          <t>0.01214659685863867 +/- 0.001897700135297471</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.0009773123909249336 +/- 0.0013856497899671356</t>
+          <t>-0.004328097731239133 +/- 0.001498841923461369</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.0014310645724258109 +/- 0.0019524420622613506</t>
+          <t>-0.00579406631762659 +/- 0.0014988419234613522</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.001570680628272214 +/- 0.0007843701589613957</t>
+          <t>-0.0015008726003490902 +/- 0.0009372231470923251</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.0050261780104711605 +/- 0.0011908357493355716</t>
+          <t>-0.010436300174520107 +/- 0.0017552936768837973</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.00017452006980799294 +/- 0.0005681961813647306</t>
+          <t>-0.0010122164048866123 +/- 0.0005046014762583364</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.00010471204188485794 +/- 0.0012589660591184326</t>
+          <t>0.001326352530540964 +/- 0.001701369299400204</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.003944153577661413 +/- 0.0023880570307989375</t>
+          <t>0.002757417102966786 +/- 0.0013648317484130509</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0019546247818498564 +/- 0.001025964290170974</t>
+          <t>-0.008307155322862159 +/- 0.0020038673779277268</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.009144851657940645 +/- 0.0023611217487312826</t>
+          <t>-0.009668411867364802 +/- 0.002256916322558782</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.00010471204188485794 +/- 0.0005188854711106085</t>
+          <t>-0.0008376963350785749 +/- 0.00027923211169285367</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.0018848167539267323 +/- 0.0006473730188827645</t>
+          <t>0.00017452006980798185 +/- 0.0004202999852981398</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.0077835951134380245 +/- 0.0014730155564404224</t>
+          <t>-0.009458987783595153 +/- 0.0012724416149080843</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.0021989528795811064 +/- 0.001439552574331672</t>
+          <t>-0.00418848167539273 +/- 0.0017452006980802671</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.00038394415357763113 +/- 0.0005507760501940494</t>
+          <t>-0.0002443280977312723 +/- 0.0003141361256544542</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.00027923211169281756 +/- 0.001166023950330892</t>
+          <t>-0.0004886561954625113 +/- 0.0006659261440956092</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.00471204188481672 +/- 0.0014242377496058026</t>
+          <t>-0.004851657940663201 +/- 0.0016844577329163915</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0011518324607329932 +/- 0.0009628701029063591</t>
+          <t>-0.0038743455497382675 +/- 0.001272441614908084</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.0016753926701570387 +/- 0.0011234538875693498</t>
+          <t>0.00020942408376959377 +/- 0.0013263525305410107</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.003071553228621249 +/- 0.0019546247818499067</t>
+          <t>-0.008237347294938958 +/- 0.0011385344803001884</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.0018150087260034643 +/- 0.0012757882640486626</t>
+          <t>-0.0017452006980803291 +/- 0.001422097646594322</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.001849912739965065 +/- 0.0012970962775610553</t>
+          <t>0.0009773123909249226 +/- 0.0006585676182936694</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0017801047120419079 +/- 0.0009552483199583843</t>
+          <t>-0.0010471204188482242 +/- 0.001404859462303542</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.0030017452006980473 +/- 0.0011059671565623059</t>
+          <t>-4.4408920985006264e-17 +/- 0.0019744691970304865</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.000802792321116963 +/- 0.0008556824203931085</t>
+          <t>-0.0035253054101222147 +/- 0.0013194455966098165</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0030017452006981028 +/- 0.0009773123909249638</t>
+          <t>-0.0018848167539267547 +/- 0.0014659685863874477</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.000314136125654485 +/- 0.00045375218150087626</t>
+          <t>-0.0005235602094241232 +/- 0.0005892475747341609</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-6.980802792319051e-05 +/- 0.0017085149389906343</t>
+          <t>-0.0025130890052356357 +/- 0.0007119049931717583</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.008167539267015734 +/- 0.0012890879799385326</t>
+          <t>-0.005479930191972127 +/- 0.001561345148086903</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0020593368237347477 +/- 0.001040701676500918</t>
+          <t>-0.0011518324607330266 +/- 0.001239461145170309</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3.490401396163412e-05 +/- 0.0017343467014038277</t>
+          <t>-0.0004537521815009216 +/- 0.0014647214840039944</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.0017801047120418524 +/- 0.0007229429381224192</t>
+          <t>0.0010471204188481132 +/- 0.0006435982169139789</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.0009773123909250115 +/- 0.00030428613916514465</t>
+          <t>-0.0002792321116928731 +/- 0.0004630540719518768</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-6.980802792320163e-05 +/- 0.00013961605584640325</t>
+          <t>-0.00013961605584643654 +/- 0.00023152703597595936</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.003979057591623059 +/- 0.0017184689179883148</t>
+          <t>-0.001570680628272292 +/- 0.002113062599325016</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.005794066317626567 +/- 0.002066128947567017</t>
+          <t>-0.0024432809773124453 +/- 0.0014972153989198753</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-0.0002443280977311946 +/- 0.0009241327954536699</t>
+          <t>-0.000523560209424101 +/- 0.0009398193380688481</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0007329842931936836 +/- 0.0015644631644687662</t>
+          <t>-0.004153577661431096 +/- 0.0014763201383983626</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.002547993019197237 +/- 0.0006253568190983914</t>
+          <t>-0.0011518324607330266 +/- 0.0013341371625561177</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.0003839441535777088 +/- 0.0004260577876346996</t>
+          <t>0.000593368237347236 +/- 0.00073298429319371</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.005828970331588157 +/- 0.0012876695808514158</t>
+          <t>-0.0008726003490401979 +/- 0.001260899955894493</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>0.007364746945898804 +/- 0.0017483392371892895</t>
+          <t>0.004677137870855086 +/- 0.0013445975765625268</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.00041884816753923193 +/- 0.0012070936450813549</t>
+          <t>-0.0035602094240838158 +/- 0.0011969583385327883</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.003350785340314111 +/- 0.001116928446771384</t>
+          <t>-0.004537521815008783 +/- 0.0009622372601808115</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-3.490401396160081e-05 +/- 0.00032928380914682944</t>
+          <t>3.490401396160081e-05 +/- 0.00010471204188480243</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.004048865619546227 +/- 0.0014824963756785595</t>
+          <t>-0.009249563699825524 +/- 0.0013719542064246876</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.0005584642233856685 +/- 0.0012985043795977719</t>
+          <t>-0.006457242582897082 +/- 0.0010954523439075253</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0010122164048865234 +/- 0.0004260577876346796</t>
+          <t>-0.0013961605584642655 +/- 0.0009748160589018437</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.0010471204188481132 +/- 0.0020050829481808264</t>
+          <t>-0.01127399650959865 +/- 0.0016743015644274197</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.005828970331588112 +/- 0.0022890753831859736</t>
+          <t>-0.003525305410122204 +/- 0.0010976743590587312</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.0024083769633507558 +/- 0.0014344658002118339</t>
+          <t>-0.003036649214659748 +/- 0.0016887916793581663</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.00017452006980804845 +/- 0.0003217991084569985</t>
+          <t>0.00010471204188478023 +/- 0.0003141361256544394</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.00024432809773120565 +/- 0.0007329842931937228</t>
+          <t>0.0004188481675392097 +/- 0.0003042861391651014</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.000663176265270482 +/- 0.0005046014762583202</t>
+          <t>0.0004537521815008216 +/- 0.0010477019909112559</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-6.980802792319051e-05 +/- 0.0003042861391651549</t>
+          <t>-0.0009424083769633996 +/- 0.0006631762652705136</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.00848167539267014 +/- 0.0018993044133211693</t>
+          <t>-0.011134380453752212 +/- 0.0014845494113882648</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.001151832460732949 +/- 0.00027260906373145825</t>
+          <t>-0.0008726003490401868 +/- 0.0003576597125989604</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.003769633507853376 +/- 0.0011867364746945901</t>
+          <t>-0.008551483420593387 +/- 0.0013359622484470763</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.006212914485165777 +/- 0.001350023009131861</t>
+          <t>-0.0038394415357766555 +/- 0.0012191447955722833</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.0005235602094240677 +/- 0.00042029998529817205</t>
+          <t>0.0024432809773123564 +/- 0.0007959339791267961</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.007399650959860371 +/- 0.0013768295234426432</t>
+          <t>-0.0028272251308900987 +/- 0.0014680447361125988</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.0007678883071552845 +/- 0.00169419352174683</t>
+          <t>-0.008376963350785405 +/- 0.001553130573213756</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.000802792321116974 +/- 0.0011261616617732582</t>
+          <t>0.009005235602094175 +/- 0.0009208311314675646</t>
         </is>
       </c>
     </row>
